--- a/mistral_translate_work/split_by_prompt/excel/ui/lang_multi_text/lang_multi_text__ui__part_0012.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/ui/lang_multi_text/lang_multi_text__ui__part_0012.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Nếu điều khiển phương tiện được đặt ở chế độ cần điều khiển, tùy chọn này sẽ theo cài đặt điều khiển thông thường.</t>
+          <t>Nếu điều khiển phương tiện được đặt ở chế độ cần gạt, tùy chọn này sẽ tuân theo cài đặt điều khiển thông thường.</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Một chiếc mô tô thám hiểm được Luuk Herssen cải tiến, trang bị module Đường Băng Mới Glacier Track. Với module này, mô tô có thể đóng băng mặt nước và di chuyển trên đó.</t>
+          <t>Một chiếc mô-tô thám hiểm được Luuk Herssen cải tiến, trang bị module Glacier Track mới. Với module này, xe có thể đóng băng mặt nước và di chuyển trên đó.</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Default</t>
+          <t>Mặc định</t>
         </is>
       </c>
     </row>
@@ -769,7 +769,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Xa</t>
+          <t>Xa xăm</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Farthest</t>
+          <t>Xa nhất</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Thiết lập khoảng cách hiển thị cho môi trường và vật thể ở xa.</t>
+          <t>Đặt khoảng cách hiển thị cho môi trường và vật thể ở xa.</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Mô tả hiện không khả dụng</t>
+          <t>Chưa có mô tả</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>&lt;color=#ac8480&gt;Bạn có thể rời Sonoro Sphere&lt;/color&gt;</t>
+          <t>&lt;color=#ac8480&gt;Bạn có thể rời khỏi Sonoro Sphere&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Map Kiểm Tra Kết Nối Mạng 1</t>
+          <t>Bản Đồ Kiểm Tra Kết Nối Mạng 1</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Map Cấu Hình Ma Nơ Canh</t>
+          <t>Bản Đồ Cấu Hình Nhân Tạo</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Map Thử Nghiệm Thế Giới</t>
+          <t>Bản đồ thử nghiệm Thế Giới</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>LV1_A_1</t>
+          <t>CẤP 1_A_1</t>
         </is>
       </c>
     </row>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Map Test Chiến đấu Tổng hợp</t>
+          <t>Bản Đồ Thử Nghiệm Chiến Đấu Tổng Hợp</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Map Kiểm Tra Cấu Hình Nhiệm Vụ</t>
+          <t>Bản Đồ Kiểm Tra Cấu Hình Nhiệm Vụ</t>
         </is>
       </c>
     </row>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Bản thử nghiệm Cơ chế Chơi</t>
+          <t>Bản Thử Nghiệm Cơ Chế Gameplay</t>
         </is>
       </c>
     </row>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Map Kiểm Tra Mẫu Tự Động</t>
+          <t>Bản Đồ Kiểm Tra Mẫu Tự Động</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Map Thử Nghiệm Combat</t>
+          <t>Bản Đồ Thử Nghiệm Chiến Đấu</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Map Kiểm Tra Bố Cục Thực Thể NPC</t>
+          <t>Bản Đồ Kiểm Tra Bố Cục NPC Entity</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Map Kiểm Tra Bố Cục SimpleNPC</t>
+          <t>Bản Đồ Kiểm Tra Bố Cục NPC Đơn Giản</t>
         </is>
       </c>
     </row>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Map Thử Thách Boss</t>
+          <t>Bản Đồ Thử Nghiệm Đầu Sỏ</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Map Thử Nghiệm NPC</t>
+          <t>Bản đồ kiểm tra NPC</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1939,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Những kẻ vô tri cản trở tiến bộ, trong khi những người vô tội phải gánh chịu thử thách áp đặt lên họ. Ngọn lửa nhen nhóm từ ký ức về một đêm xa xôi, được tiếp sức bởi hoàn cảnh hiện tại, thắp lên nỗi đau quá khứ của Scar và sự tái sinh của những tư tưởng mới, cuối cùng dẫn đến sự sụp đổ của trật tự thế giới cũ.</t>
+          <t>Kẻ ngu muội cản trở tiến bộ, còn người vô tội phải gánh chịu những thử thách áp đặt lên họ. Ngọn lửa nhen nhóm từ ký ức về một đêm xa xưa, được thổi bùng bởi hoàn cảnh hiện tại, đốt cháy nỗi đau quá khứ của Scar và sự hồi sinh của những tư tưởng mới, cuối cùng dẫn đến sự sụp đổ của trật tự thế giới cũ.</t>
         </is>
       </c>
     </row>
@@ -2004,7 +2004,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Sa Đọa Suy Vong</t>
+          <t>Sự Suy Đồi Tội Lỗi</t>
         </is>
       </c>
     </row>
@@ -2070,8 +2070,8 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Jinzhou là nơi đặt một trong những trung tâm cơ sở dữ liệu độc đáo của Huanglong, được quản lý bởi Sentinel và kiểm soát bởi Tri Huyện Jinzhou. Nó sử dụng thời gian làm chỉ mục và ghi chép chính xác các thông tin liên quan đến sự thành lập của thành phố, tạo nên một nguồn tài nguyên toàn diện và khách quan. Các bộ sách giáo khoa của Jinzhou, được lưu trữ tại Tòa Thị Chính, chứa đựng những dữ liệu quan trọng được thu thập từ thời xa xưa. Cơ sở dữ liệu khổng lồ này chứa đựng câu trả lời cho bất kỳ câu hỏi nào về lịch sử của Huanglong.
-Mức độ nhân vật đề xuất: Cấp 40</t>
+          <t>Tấn Châu là nơi lưu giữ một trong những trung tâm dữ liệu độc đáo của Huanglong, do Sentinel quản lý và dưới sự kiểm soát của Tri phủ Tấn Châu. Hệ thống này lấy thời gian làm chỉ mục và ghi chép chính xác mọi thông tin liên quan đến sự hình thành của thành phố, tạo nên một nguồn tài nguyên toàn diện và khách quan. Những cuốn sách lớp của Tấn Châu, được lưu trữ tại Tòa Thị chính, chứa đựng dữ liệu quan trọng được thu thập từ thời xa xưa. Kho dữ liệu khổng lồ này ẩn chứa câu trả lời cho mọi thắc mắc về lịch sử Huanglong.
+Cấp độ nhân vật đề xuất: Cấp 40</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Thư viện Hoàng Gia</t>
+          <t>Thư Viện Hoàng Gia</t>
         </is>
       </c>
     </row>
@@ -2201,7 +2201,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Bóng tối của quá khứ đang phủ xuống đã sẵn sàng vũ khí, chờ đợi một kẻ thách thức. Đã đến lúc ngọn lửa chiến tranh phải tắt.</t>
+          <t>Bóng ma quá khứ đã sẵn sàng vũ khí, chờ đợi một kẻ thách thức. Đã đến lúc ngọn lửa chiến tranh phải tắt.</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Thanh Kiếm Từ Trên Cao</t>
+          <t>Lưỡi Kiếm Từ Trên Cao</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Map Thử Nghiệm Tacet</t>
+          <t>Bản Đồ Kiểm Tra Tổ Tacet</t>
         </is>
       </c>
     </row>
@@ -2461,7 +2461,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Bản đồ Kiểm tra Kết nối Mạng</t>
+          <t>Bản Đồ Kiểm Tra Kết Nối Mạng</t>
         </is>
       </c>
     </row>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Map Thử Nghiệm Dịch Chuyển Nhanh (chơi đơn)</t>
+          <t>Bản đồ Thử nghiệm Dịch chuyển Nhanh (Chơi đơn)</t>
         </is>
       </c>
     </row>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Khu vực Rủi Ro Thấp-Tháp I-Cấp I</t>
+          <t>Khu Vực Rủi Ro Thấp - Tháp I - Tầng I</t>
         </is>
       </c>
     </row>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Khu vực Rủi Ro Thấp-Tháp I-Cấp I</t>
+          <t>Khu Vực Rủi Ro Thấp - Tháp I - Tầng I</t>
         </is>
       </c>
     </row>
@@ -2721,7 +2721,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Khu vực Rủi Ro Thấp-Tháp I-Cấp II</t>
+          <t>Khu Vực Rủi Ro Thấp - Tháp I - Tầng II</t>
         </is>
       </c>
     </row>
@@ -2786,7 +2786,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Khu vực Rủi Ro Thấp-Tháp I-Cấp II</t>
+          <t>Khu Vực Rủi Ro Thấp - Tháp I - Tầng II</t>
         </is>
       </c>
     </row>
@@ -2851,7 +2851,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Khu vực Rủi Ro Thấp-Tháp I-Cấp III</t>
+          <t>Khu Vực Rủi Ro Thấp - Tháp I - Tầng III</t>
         </is>
       </c>
     </row>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Khu vực Rủi Ro Thấp-Tháp I-Cấp III</t>
+          <t>Khu Vực Rủi Ro Thấp - Tháp I - Tầng III</t>
         </is>
       </c>
     </row>
@@ -2981,7 +2981,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Khu vực Rủi Ro Thấp-Tháp I-Cấp IV</t>
+          <t>Khu vực nguy hiểm thấp - Tháp I - Cấp IV</t>
         </is>
       </c>
     </row>
@@ -3046,7 +3046,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Khu vực Rủi Ro Thấp-Tháp I-Cấp IV</t>
+          <t>Khu vực nguy hiểm thấp - Tháp I - Cấp IV</t>
         </is>
       </c>
     </row>
@@ -3111,7 +3111,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Khu vực Rủi Ro Cao-Tháp I-Cấp I</t>
+          <t>Khu vực nguy hiểm - Tháp I - Cấp I</t>
         </is>
       </c>
     </row>
@@ -3176,7 +3176,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Khu vực Rủi Ro Cao-Tháp I-Cấp I</t>
+          <t>Khu vực nguy hiểm - Tháp I - Cấp I</t>
         </is>
       </c>
     </row>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Khu vực Rủi Ro Cao-Tháp I-Cấp II</t>
+          <t>Khu vực nguy hiểm - Tháp I - Cấp II</t>
         </is>
       </c>
     </row>
@@ -3306,7 +3306,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Khu vực Rủi Ro Cao-Tháp I-Cấp II</t>
+          <t>Khu vực nguy hiểm - Tháp I - Cấp II</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Khu vực nguy hiểm cao-Tháp I-Cấp III</t>
+          <t>Khu vực nguy hiểm - Tháp I - Cấp III</t>
         </is>
       </c>
     </row>
@@ -3436,7 +3436,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Khu vực nguy hiểm cao-Tháp I-Cấp III</t>
+          <t>Khu vực nguy hiểm - Tháp I - Cấp III</t>
         </is>
       </c>
     </row>
@@ -3501,7 +3501,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Khu vực nguy hiểm cao-Tháp I-Cấp IV</t>
+          <t>Khu vực nguy hiểm - Tháp I - Cấp IV</t>
         </is>
       </c>
     </row>
@@ -3566,7 +3566,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Khu vực nguy hiểm cao-Tháp I-Cấp IV</t>
+          <t>Khu vực nguy hiểm - Tháp I - Cấp IV</t>
         </is>
       </c>
     </row>
@@ -3631,7 +3631,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Khu vực nguy hiểm cao-Tháp II-Cấp I</t>
+          <t>Khu vực nguy hiểm - Tháp II - Cấp I</t>
         </is>
       </c>
     </row>
@@ -3696,7 +3696,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Khu vực nguy hiểm cao-Tháp II-Cấp I</t>
+          <t>Khu vực nguy hiểm - Tháp II - Cấp I</t>
         </is>
       </c>
     </row>
@@ -3761,7 +3761,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Khu vực nguy hiểm cao-Tháp II-Cấp II</t>
+          <t>Khu vực nguy hiểm - Tháp II - Cấp II</t>
         </is>
       </c>
     </row>
@@ -3826,7 +3826,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Khu vực nguy hiểm cao-Tháp II-Cấp II</t>
+          <t>Khu vực nguy hiểm - Tháp II - Cấp II</t>
         </is>
       </c>
     </row>
@@ -3891,7 +3891,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Khu vực nguy hiểm cao-Tháp II-Cấp III</t>
+          <t>Khu vực nguy hiểm - Tháp II - Cấp III</t>
         </is>
       </c>
     </row>
@@ -3956,7 +3956,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Khu vực nguy hiểm cao-Tháp II-Cấp III</t>
+          <t>Khu vực nguy hiểm - Tháp II - Cấp III</t>
         </is>
       </c>
     </row>
@@ -4021,7 +4021,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Khu vực nguy hiểm cao-Tháp II-Cấp IV</t>
+          <t>Khu vực nguy hiểm - Tháp II - Cấp IV</t>
         </is>
       </c>
     </row>
@@ -4086,7 +4086,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Khu vực nguy hiểm cao-Tháp II-Cấp IV</t>
+          <t>Khu vực nguy hiểm - Tháp II - Cấp IV</t>
         </is>
       </c>
     </row>
@@ -4151,7 +4151,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>V1-1-1</t>
+          <t>Ta đã tìm thấy ngươi rồi, Vận Mệnh Giả.</t>
         </is>
       </c>
     </row>
@@ -4216,7 +4216,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>V1-1-1</t>
+          <t>Ta đã tìm thấy ngươi rồi, Vận Mệnh Giả.</t>
         </is>
       </c>
     </row>
@@ -4281,7 +4281,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>V1-1-2</t>
+          <t>Ngươi không thể trốn khỏi Tổ Tacet này đâu.</t>
         </is>
       </c>
     </row>
@@ -4346,7 +4346,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>V1-1-2</t>
+          <t>Ngươi không thể trốn khỏi Tổ Tacet này đâu.</t>
         </is>
       </c>
     </row>
@@ -4411,7 +4411,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Phiên bản 1-1-3</t>
+          <t>Hãy thức tỉnh đi... và đối mặt với số phận của mình.</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Phiên bản 1-1-3</t>
+          <t>Hãy thức tỉnh đi... và đối mặt với số phận của mình.</t>
         </is>
       </c>
     </row>
@@ -4541,7 +4541,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>V1-1-4</t>
+          <t>Tần số của ngươi đang dao động... Đừng chống cự nữa.</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>V1-1-4</t>
+          <t>Tần số của ngươi đang dao động... Đừng chống cự nữa.</t>
         </is>
       </c>
     </row>
@@ -4671,7 +4671,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>V1-2-1</t>
+          <t>Lại một Cộng Hưởng Giả nữa sao? Số phận thật tàn nhẫn...</t>
         </is>
       </c>
     </row>
@@ -4736,7 +4736,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>V1-2-1</t>
+          <t>Lại một Cộng Hưởng Giả nữa sao? Số phận thật tàn nhẫn...</t>
         </is>
       </c>
     </row>
@@ -4801,7 +4801,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>V1-2-2</t>
+          <t>Ngươi đến đây để tìm gì? Sự thật hay là cái chết?</t>
         </is>
       </c>
     </row>
@@ -4866,7 +4866,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>V1-2-2</t>
+          <t>Ngươi đến đây để tìm gì? Sự thật hay là cái chết?</t>
         </is>
       </c>
     </row>
@@ -4931,7 +4931,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>V1-2-3</t>
+          <t>Tacet Discord... chúng đang chờ đợi ngươi.</t>
         </is>
       </c>
     </row>
@@ -4996,7 +4996,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>V1-2-3</t>
+          <t>Tacet Discord... chúng đang chờ đợi ngươi.</t>
         </is>
       </c>
     </row>
@@ -5061,7 +5061,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>V1-2-IV</t>
+          <t>IV:::Hãy nhớ lấy... mọi thứ ở đây đều là ảo ảnh.</t>
         </is>
       </c>
     </row>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>V1-2-IV</t>
+          <t>IV:::Hãy nhớ lấy... mọi thứ ở đây đều là ảo ảnh.</t>
         </is>
       </c>
     </row>
@@ -5191,7 +5191,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>V1-3-I</t>
+          <t>I:::Ngươi không cô đơn đâu, nhưng cũng đừng tin ai quá dễ dàng.</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>V1-3-I</t>
+          <t>I:::Ngươi không cô đơn đâu, nhưng cũng đừng tin ai quá dễ dàng.</t>
         </is>
       </c>
     </row>
@@ -5321,7 +5321,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>V1-3-II</t>
+          <t>II:::Sức mạnh của ngươi... thật đáng sợ.</t>
         </is>
       </c>
     </row>
@@ -5386,7 +5386,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>V1-3-II</t>
+          <t>II:::Sức mạnh của ngươi... thật đáng sợ.</t>
         </is>
       </c>
     </row>
@@ -5451,7 +5451,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>V1-3-III</t>
+          <t>III:::Đừng để Tổ Tacet nuốt chửng linh hồn ngươi.</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>V1-3-III</t>
+          <t>III:::Đừng để Tổ Tacet nuốt chửng linh hồn ngươi.</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>V1-3-IV</t>
+          <t>IV:::Cuối cùng, ngươi cũng đã đến... nơi này.</t>
         </is>
       </c>
     </row>
@@ -5646,7 +5646,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>V1-3-IV</t>
+          <t>IV:::Cuối cùng, ngươi cũng đã đến... nơi này.</t>
         </is>
       </c>
     </row>
@@ -5711,7 +5711,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>LVIII_C_I</t>
+          <t>LVIII_C_I:::Ta đã thấy tương lai của Solaris-3... và nó chỉ toàn là tro tàn.</t>
         </is>
       </c>
     </row>
@@ -5776,7 +5776,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>LVIII_C_I</t>
+          <t>LVIII_C_I:::Ta đã thấy tương lai của Solaris-3... và nó chỉ toàn là tro tàn.</t>
         </is>
       </c>
     </row>
@@ -5841,7 +5841,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>LVIII_C_II</t>
+          <t>LVIII_C_II:::Ngươi không hiểu đâu, Rover. Số phận này đã được định sẵn từ lâu.</t>
         </is>
       </c>
     </row>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>LVIII_C_II</t>
+          <t>LVIII_C_II:::Ngươi không hiểu đâu, Rover. Số phận này đã được định sẵn từ lâu.</t>
         </is>
       </c>
     </row>
@@ -5971,7 +5971,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>LVIII_C_III</t>
+          <t>LVIII_C_III:::Nhưng nếu ngươi dám chống lại nó... ta sẽ không khoan nhượng.</t>
         </is>
       </c>
     </row>
@@ -6036,7 +6036,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>LVIII_C_III</t>
+          <t>LVIII_C_III:::Nhưng nếu ngươi dám chống lại nó... ta sẽ không khoan nhượng.</t>
         </is>
       </c>
     </row>
@@ -6101,7 +6101,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>LVIV_A_I</t>
+          <t>LVIV_A_I:::Chúng ta không thể cứ mãi chạy trốn được.</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>LVIV_A_I</t>
+          <t>LVIV_A_I:::Chúng ta không thể cứ mãi chạy trốn được.</t>
         </is>
       </c>
     </row>
@@ -6231,7 +6231,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>LVIV_A_II</t>
+          <t>LVIV_A_II:::Mỗi bước chân đều kéo theo những tiếng thì thầm của Tổ Tacet...</t>
         </is>
       </c>
     </row>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>LVIV_A_II</t>
+          <t>LVIV_A_II:::Mỗi bước chân đều kéo theo những tiếng thì thầm của Tổ Tacet...</t>
         </is>
       </c>
     </row>
@@ -6361,7 +6361,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>LVIV_A_III</t>
+          <t>LVIV_A_III:::Nhưng nếu chúng ta không bước tiếp, thì ai sẽ làm?</t>
         </is>
       </c>
     </row>
@@ -6426,7 +6426,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>LVIV_A_III</t>
+          <t>LVIV_A_III:::Nhưng nếu chúng ta không bước tiếp, thì ai sẽ làm?</t>
         </is>
       </c>
     </row>
@@ -6491,7 +6491,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>LVIV_B_I</t>
+          <t>LVIV_B_I:::Nghe này, {PlayerName}... cậu có bao giờ cảm thấy mình chỉ là một con tốt trong bàn cờ này không?</t>
         </is>
       </c>
     </row>
@@ -6556,7 +6556,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>LVIV_B_I</t>
+          <t>LVIV_B_I:::Nghe này, {PlayerName}... cậu có bao giờ cảm thấy mình chỉ là một con tốt trong bàn cờ này không?</t>
         </is>
       </c>
     </row>
@@ -6621,7 +6621,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>LVIV_B_II</t>
+          <t>LVIV_B_II:::Mọi người đều nói về "số phận", nhưng chẳng ai thèm hỏi ý kiến ta cả.</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>LVIV_B_II</t>
+          <t>LVIV_B_II:::Mọi người đều nói về "số phận", nhưng chẳng ai thèm hỏi ý kiến ta cả.</t>
         </is>
       </c>
     </row>
@@ -6751,7 +6751,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>LVIV_B_III</t>
+          <t>LVIV_B_III:::Nếu vậy... ta sẽ tự mình phá vỡ bàn cờ.</t>
         </is>
       </c>
     </row>
@@ -6816,7 +6816,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>LVIV_B_III</t>
+          <t>LVIV_B_III:::Nếu vậy... ta sẽ tự mình phá vỡ bàn cờ.</t>
         </is>
       </c>
     </row>
@@ -6881,7 +6881,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>LVIV_C_I</t>
+          <t>LVIV_C_I:::Tần số của chúng ta đang dần mất ổn định...</t>
         </is>
       </c>
     </row>
@@ -6946,7 +6946,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>LVIV_C_I</t>
+          <t>LVIV_C_I:::Tần số của chúng ta đang dần mất ổn định...</t>
         </is>
       </c>
     </row>
@@ -7011,7 +7011,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>LVIV_C_II</t>
+          <t>LVIV_C_II:::Những Cộng Hưởng Giả khác đã bắt đầu dao động. Họ không còn tin vào hy vọng nữa.</t>
         </is>
       </c>
     </row>
@@ -7076,7 +7076,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>LVIV_C_II</t>
+          <t>LVIV_C_II:::Những Cộng Hưởng Giả khác đã bắt đầu dao động. Họ không còn tin vào hy vọng nữa.</t>
         </is>
       </c>
     </row>
@@ -7141,7 +7141,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>LVIV_C_III</t>
+          <t>LVIV_C_III:::Nhưng cậu... cậu vẫn còn giữ được ngọn lửa trong lòng, phải không?</t>
         </is>
       </c>
     </row>
@@ -7206,7 +7206,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>LVIV_C_III</t>
+          <t>LVIV_C_III:::Nhưng cậu... cậu vẫn còn giữ được ngọn lửa trong lòng, phải không?</t>
         </is>
       </c>
     </row>
@@ -7271,7 +7271,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Bài Kiểm Tra Hiệu Suất-VI Map Quái Small</t>
+          <t>Bản Đồ Quái Vật Nhỏ - Kiểm Tra Hiệu Suất VI</t>
         </is>
       </c>
     </row>
@@ -7336,7 +7336,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Trong Sonoro Sphere, một khu rừng sương mù bí ẩn, ẩn chứa các Vật Phẩm Tăng Cường Character và Vũ Khí mang hiệu ứng Waveworn.</t>
+          <t>Trong Sonoro Sphere, một khu rừng sương mù bí ẩn, ẩn chứa các vật phẩm Tăng Cường Nhân Vật và Vũ Khí mang hiệu ứng Waveworn.</t>
         </is>
       </c>
     </row>
@@ -7401,7 +7401,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Misty Andante: Helix</t>
+          <t>Sương Mù Andante: Xoắn Ốc</t>
         </is>
       </c>
     </row>
@@ -7466,7 +7466,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Khi đánh trúng kẻ địch, Basic Attack giảm Cooldown của Resonance Liberation đi 1 giây, kích hoạt tối đa 1 lần mỗi giây.</t>
+          <t>Khi đánh trúng kẻ địch, Đòn Basic Attack giảm Thời gian hồi Chiêu của Resonance Liberation đi 1 giây, kích hoạt tối đa 1 lần mỗi giây.</t>
         </is>
       </c>
     </row>
@@ -7531,7 +7531,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Bên trong Sonoro Sphere, một khu rừng tuyệt đẹp được ánh trăng chiếu sáng, ẩn chứa các Vật Phẩm Tăng Cường Character và Vũ Khí mang hiệu ứng Waveworn.</t>
+          <t>Trong Sonoro Sphere, một khu rừng tuyệt đẹp được ánh trăng chiếu rọi, ẩn chứa các vật phẩm Tăng Cường Nhân Vật và Vũ Khí mang hiệu ứng Waveworn.</t>
         </is>
       </c>
     </row>
@@ -7596,7 +7596,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Lightseeker: Cadence Flora</t>
+          <t>Kẻ Tìm Ánh Sáng: Cadence Flora</t>
         </is>
       </c>
     </row>
@@ -7661,7 +7661,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Fusion DMG tăng 25%.</t>
+          <t>Tăng Sát Thương Fusion lên 25%.</t>
         </is>
       </c>
     </row>
@@ -7726,7 +7726,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Những kẻ vô tri cản trở tiến bộ, trong khi những người vô tội phải gánh chịu thử thách áp đặt lên họ. Ngọn lửa nhen nhóm từ ký ức về một đêm xa xôi, được tiếp sức bởi hoàn cảnh hiện tại, thắp lên nỗi đau quá khứ của Scar và sự tái sinh của những tư tưởng mới, cuối cùng dẫn đến sự sụp đổ của trật tự thế giới cũ.</t>
+          <t>Kẻ ngu muội cản trở tiến bộ, còn người vô tội phải gánh chịu những thử thách áp đặt lên họ. Ngọn lửa nhen nhóm từ ký ức về một đêm xa xưa, được thổi bùng bởi hoàn cảnh hiện tại, đốt cháy nỗi đau quá khứ của Scar và sự hồi sinh của những tư tưởng mới, cuối cùng dẫn đến sự sụp đổ của trật tự thế giới cũ.</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Mở khóa ở Giai đoạn SOL3 1</t>
+          <t>Mở khóa ở Giai Đoạn SOL3 1</t>
         </is>
       </c>
     </row>
@@ -7856,7 +7856,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Thử thách Hàng tuần: Sa Đọa Suy Vong</t>
+          <t>Thử Thách Hàng Tuần: Sa Đọa Suy Vong</t>
         </is>
       </c>
     </row>
@@ -7921,7 +7921,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Mở khóa ở Giai đoạn SOL3 2</t>
+          <t>Mở khóa ở Giai Đoạn SOL3 2</t>
         </is>
       </c>
     </row>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Mở khóa ở Giai đoạn SOL3 3</t>
+          <t>Mở khóa ở Giai Đoạn SOL3 3</t>
         </is>
       </c>
     </row>
@@ -8051,7 +8051,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Mở khóa ở Giai đoạn SOL3 4</t>
+          <t>Mở khóa ở Giai Đoạn SOL3 4</t>
         </is>
       </c>
     </row>
@@ -8116,7 +8116,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Mở khóa ở Giai đoạn SOL3 5</t>
+          <t>Mở khóa ở Giai Đoạn SOL3 5</t>
         </is>
       </c>
     </row>
@@ -8181,7 +8181,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Mở khóa ở Giai đoạn SOL3 6</t>
+          <t>Mở khóa ở Giai Đoạn SOL3 6</t>
         </is>
       </c>
     </row>
@@ -8246,7 +8246,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Mở khóa ở Giai đoạn SOL3 7</t>
+          <t>Mở khóa ở Giai Đoạn SOL3 7</t>
         </is>
       </c>
     </row>
@@ -8311,7 +8311,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Mở khóa ở Giai đoạn SOL3 8</t>
+          <t>Mở khóa ở Giai Đoạn SOL3 8</t>
         </is>
       </c>
     </row>
@@ -8376,7 +8376,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Thử thách Hàng tuần: Thanh Kiếm Từ Trên Cao</t>
+          <t>Thử Thách Hàng Tuần: Kiếm Sĩ Từ Trên Cao</t>
         </is>
       </c>
     </row>
@@ -8442,8 +8442,8 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Lửa chưa tắt hẳn, nhưng ký ức vẫn còn.
-Khi bạn quay lại nơi này, thảm họa cộng hưởng và ký ức về trận chiến với "lưỡi kiếm" lại ùa về.</t>
+          <t>Lửa chưa tắt hẳn, nhưng ký ức vẫn còn đó.
+Khi cậu bước vào nơi này lần nữa, thảm họa lại vang vọng và ký ức về trận chiến với những "lưỡi kiếm" ùa về.</t>
         </is>
       </c>
     </row>
@@ -8508,7 +8508,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Trong Sonoro Sphere, một khu rừng tuyệt đẹp tồn tại ở ranh giới giữa ngày và đêm, ẩn chứa các vật phẩm Tăng Cường Character và Vũ Khí mang hiệu ứng Waveworn.</t>
+          <t>Trong Sonoro Sphere, một khu rừng tuyệt đẹp nằm ở ranh giới giữa ngày và đêm, ẩn chứa các vật phẩm Tăng Cường Nhân Vật và Vũ Khí mang hiệu ứng Waveworn.</t>
         </is>
       </c>
     </row>
@@ -8573,7 +8573,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Crystallized Flame: Phlogiston</t>
+          <t>Lửa Kết Tinh: Phlogiston</t>
         </is>
       </c>
     </row>
@@ -8703,7 +8703,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Map thử nghiệm Fast Travel (Hợp tác)</t>
+          <t>Bản đồ Thử nghiệm Dịch chuyển Nhanh (Chơi cùng)</t>
         </is>
       </c>
     </row>
@@ -8768,7 +8768,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Bản thử nghiệm Âm thanh</t>
+          <t>Mức Kiểm Tra Âm Thanh</t>
         </is>
       </c>
     </row>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Map Thử Nghiệm Động Vật</t>
+          <t>Bản Đồ Thử Nghiệm Động Vật</t>
         </is>
       </c>
     </row>
@@ -8898,7 +8898,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Mẫu Thế Giới Domain</t>
+          <t>Mẫu Vùng Thế Giới</t>
         </is>
       </c>
     </row>
@@ -8963,7 +8963,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Mẫu Thế Giới Domain</t>
+          <t>Mẫu Vùng Thế Giới</t>
         </is>
       </c>
     </row>
@@ -9028,7 +9028,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Huaxu Academy là trung tâm nghiên cứu khoa học của Jinzhou. Là một chi nhánh của Huaxu Academy Huanglong danh tiếng, nơi đây sở hữu truyền thống học thuật lâu đời và ưu tiên phát triển khoa học công nghệ. Nằm ở tiền tuyến chống lại Tacet Discord, học viện đóng vai trò quan trọng trong nỗ lực chiến tranh.</t>
+          <t>Học viện Huaxu là trung tâm nghiên cứu khoa học của Jinzhou. Là chi nhánh của Học viện Huanglong Huaxu lừng danh, nơi đây thừa hưởng di sản học thuật phong phú và luôn ưu tiên những tiến bộ khoa học công nghệ. Nằm trên tiền tuyến chống lại Tacet Discord, Học viện đóng vai trò then chốt trong cuộc chiến đang diễn ra.</t>
         </is>
       </c>
     </row>
@@ -9158,7 +9158,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>test Map Thử Nghiệm</t>
+          <t>Bản đồ thử nghiệm</t>
         </is>
       </c>
     </row>
@@ -9223,7 +9223,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Map TD-UniverseEditor</t>
+          <t>Bản đồ TD-UniverseEditor</t>
         </is>
       </c>
     </row>
@@ -9288,7 +9288,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Map Thử Nghiệm Vực New (chơi đơn)</t>
+          <t>Bản Đồ Thử Thách Lĩnh Vực Mới (chơi đơn)</t>
         </is>
       </c>
     </row>
@@ -9353,7 +9353,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Map thử nghiệm Lĩnh vực Phòng thủ (chơi đơn)</t>
+          <t>Bản Đồ Kiểm Tra Phòng Ngự (chơi đơn)</t>
         </is>
       </c>
     </row>
@@ -9418,7 +9418,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Bản thử nghiệm (bắt quái)</t>
+          <t>Cấp Độ Kiểm Tra (bắt quái)</t>
         </is>
       </c>
     </row>
@@ -9483,7 +9483,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Bản thử nghiệm Cây Domain Đồng đội</t>
+          <t>Cây Thử nghiệm Tổ Tacet Đồng Đội</t>
         </is>
       </c>
     </row>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Bản thử nghiệm Đồng đội CE</t>
+          <t>Kiểm tra Hợp Tác CE</t>
         </is>
       </c>
     </row>
@@ -9613,7 +9613,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Trong Sonoro Sphere, một cảnh quan đầy hiểm nguy của những tàn tích nóng chảy, ẩn chứa các vật phẩm Tăng Cấp Character và Vũ Khí mang hiệu ứng Waveworn.</t>
+          <t>Trong Sonoro Sphere, một vùng đất nguy hiểm với những tàn tích nóng chảy, ẩn chứa các vật phẩm Tăng Cường Nhân Vật và Vũ Khí mang hiệu ứng Waveworn.</t>
         </is>
       </c>
     </row>
@@ -9678,7 +9678,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Core Nóng Chảy: Nhuộm Kim</t>
+          <t>Lõi Nóng Chảy: Nhũ Kim</t>
         </is>
       </c>
     </row>
@@ -9743,7 +9743,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>DMG của Outro Skill tăng 100%.</t>
+          <t>Sát Thương Kỹ Năng Hồi Kết tăng thêm 100%</t>
         </is>
       </c>
     </row>
@@ -9808,7 +9808,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Trong Sonoro Sphere, một vùng đất nguy hiểm với vô số bẫy chết người, ẩn chứa các vật phẩm Tăng cường Nhân vật và Weapon mang hiệu ứng Waveworn.</t>
+          <t>Trong Sonoro Sphere, một địa hình hiểm trở đầy bẫy chết người, ẩn chứa các vật phẩm Tăng Cường Nhân Vật và Vũ Khí mang hiệu ứng Waveworn.</t>
         </is>
       </c>
     </row>
@@ -9873,7 +9873,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Giai đoạn Ăn mòn: Waveworn Residue</t>
+          <t>Giai Đoạn Ăn Mòn: Cặn Sóng Tàn Tích</t>
         </is>
       </c>
     </row>
@@ -9938,7 +9938,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>DMG và DEF của đội tăng 25% khi sử dụng Resonance Liberation, kéo dài 15 giây và cộng dồn tối đa 3 lần.</t>
+          <t>Khi sử dụng Resonance Liberation, DMG và phòng ngự của đội tăng 25%, hiệu ứng kéo dài 15 giây và có thể chồng chất tối đa 3 lần.</t>
         </is>
       </c>
     </row>
@@ -10003,7 +10003,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>TD - Bản thử nghiệm Tương tác</t>
+          <t>TD - Kiểm tra tương tác</t>
         </is>
       </c>
     </row>
@@ -10068,7 +10068,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Crownless - Cấp 55</t>
+          <t>Cấp độ Crownless-55</t>
         </is>
       </c>
     </row>
@@ -10133,7 +10133,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>Crownless - Cấp 55</t>
+          <t>Cấp độ Crownless-55</t>
         </is>
       </c>
     </row>
@@ -10198,7 +10198,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Crownless - Lv. 50</t>
+          <t>Crownless - Cấp 50</t>
         </is>
       </c>
     </row>
@@ -10263,7 +10263,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Crownless - Lv. 50</t>
+          <t>Crownless - Cấp 50</t>
         </is>
       </c>
     </row>
@@ -10458,7 +10458,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Crownless I - Lv. 50</t>
+          <t>Crownless I - Cấp 50</t>
         </is>
       </c>
     </row>
@@ -10523,7 +10523,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Crownless I - Lv. 50</t>
+          <t>Crownless I - Cấp 50</t>
         </is>
       </c>
     </row>
@@ -10588,7 +10588,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>Tempest Mephis I - Cấp 60</t>
+          <t>Mephis Bão Tố I - Cấp 60</t>
         </is>
       </c>
     </row>
@@ -10653,7 +10653,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>Tempest Mephis I - Cấp 60</t>
+          <t>Mephis Bão Tố I - Cấp 60</t>
         </is>
       </c>
     </row>
@@ -10718,7 +10718,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Tempest Mephis I - Cấp 60</t>
+          <t>Mephis Bão Tố I - Cấp 60</t>
         </is>
       </c>
     </row>
@@ -11108,7 +11108,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Lampylumen Myriad - Cấp 60</t>
+          <t>Lampylumen Myriad - Lv. 60</t>
         </is>
       </c>
     </row>
@@ -11173,7 +11173,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>Lampylumen Myriad - Cấp 60</t>
+          <t>Lampylumen Myriad - Lv. 60</t>
         </is>
       </c>
     </row>
@@ -11238,7 +11238,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Mourning Aix - Lv. 50</t>
+          <t>Aix Tang Tóc - Cấp 50</t>
         </is>
       </c>
     </row>
@@ -11303,7 +11303,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Mourning Aix - Lv. 50</t>
+          <t>Aix Tang Tóc - Cấp 50</t>
         </is>
       </c>
     </row>
@@ -11498,7 +11498,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>Mech Abomination - Lv. 50</t>
+          <t>Quái Thú Cơ Khí - Cấp 50</t>
         </is>
       </c>
     </row>
@@ -11563,7 +11563,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>Mech Abomination - Lv. 50</t>
+          <t>Quái Thú Cơ Khí - Cấp 50</t>
         </is>
       </c>
     </row>
@@ -11628,7 +11628,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>Mech Abomination - Cấp 60</t>
+          <t>Quái Thú Cơ Khí - Cấp 60</t>
         </is>
       </c>
     </row>
@@ -11693,7 +11693,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>Mech Abomination - Cấp 60</t>
+          <t>Quái Thú Cơ Khí - Cấp 60</t>
         </is>
       </c>
     </row>
@@ -11758,7 +11758,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>Impermanence Heron - Lv. 50</t>
+          <t>Heron Vô Thường - Cấp 50</t>
         </is>
       </c>
     </row>
@@ -11823,7 +11823,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>Impermanence Heron - Lv. 50</t>
+          <t>Heron Vô Thường - Cấp 50</t>
         </is>
       </c>
     </row>
@@ -11888,7 +11888,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>Impermanence Heron - Cấp 60</t>
+          <t>Heron Vô Thường - Cấp 60</t>
         </is>
       </c>
     </row>
@@ -11953,7 +11953,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>Impermanence Heron - Cấp 60</t>
+          <t>Heron Vô Thường - Cấp 60</t>
         </is>
       </c>
     </row>
@@ -12018,7 +12018,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>Scar - Cấp 60</t>
+          <t>Vết Sẹo - Cấp 60</t>
         </is>
       </c>
     </row>
@@ -12083,7 +12083,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>Scar - Cấp 60</t>
+          <t>Vết Sẹo - Cấp 60</t>
         </is>
       </c>
     </row>
@@ -12148,7 +12148,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>Sẹo: Giai đoạn II - Cấp 50</t>
+          <t>Scar: Giai Đoạn II - Cấp 50</t>
         </is>
       </c>
     </row>
@@ -12213,7 +12213,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>Sẹo: Giai đoạn II - Cấp 50</t>
+          <t>Scar: Giai Đoạn II - Cấp 50</t>
         </is>
       </c>
     </row>
@@ -12278,7 +12278,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>Sẹo: Giai đoạn II - Cấp 60</t>
+          <t>Scar: Giai Đoạn II - Cấp 60</t>
         </is>
       </c>
     </row>
@@ -12343,7 +12343,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>Sẹo: Giai đoạn II - Cấp 60</t>
+          <t>Scar: Giai Đoạn II - Cấp 60</t>
         </is>
       </c>
     </row>
@@ -12408,7 +12408,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>Inferno Rider - Lv. 55</t>
+          <t>Kỵ Sĩ Hỏa Ngục - Cấp 55</t>
         </is>
       </c>
     </row>
@@ -12473,7 +12473,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>Inferno Rider - Lv. 55</t>
+          <t>Kỵ Sĩ Hỏa Ngục - Cấp 55</t>
         </is>
       </c>
     </row>
@@ -12538,7 +12538,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>Inferno Rider - Cấp 65</t>
+          <t>Kỵ Sĩ Hỏa Ngục - Cấp 65</t>
         </is>
       </c>
     </row>
@@ -12603,7 +12603,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Inferno Rider - Cấp 65</t>
+          <t>Kỵ Sĩ Hỏa Ngục - Cấp 65</t>
         </is>
       </c>
     </row>
@@ -12668,7 +12668,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>Inferno Rider - Lv. 70</t>
+          <t>Kỵ Sĩ Hỏa Ngục - Cấp 70</t>
         </is>
       </c>
     </row>
@@ -12733,7 +12733,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Inferno Rider - Lv. 70</t>
+          <t>Kỵ Sĩ Hỏa Ngục - Cấp 70</t>
         </is>
       </c>
     </row>
@@ -12798,7 +12798,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>Inferno Rider - Cấp 65</t>
+          <t>Kỵ Sĩ Hỏa Ngục - Cấp 65</t>
         </is>
       </c>
     </row>
@@ -12863,7 +12863,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Inferno Rider - Cấp 65</t>
+          <t>Kỵ Sĩ Hỏa Ngục - Cấp 65</t>
         </is>
       </c>
     </row>
@@ -12928,7 +12928,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>Lưỡi Hái Bay Gori - Cấp 55</t>
+          <t>Lưỡi Hái Bay của Gori - Cấp 55</t>
         </is>
       </c>
     </row>
@@ -12993,7 +12993,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>Crownless - Bản thử nghiệm Đồng đội</t>
+          <t>Crownless - Thử Nghiệm Đồng Đội</t>
         </is>
       </c>
     </row>
@@ -13448,7 +13448,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Lampylumen Myriad - Hạng 65</t>
+          <t>Lampylumen Myriad - Lớp 65</t>
         </is>
       </c>
     </row>
@@ -13513,7 +13513,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Lampylumen Myriad - Hạng 65</t>
+          <t>Lampylumen Myriad - Lớp 65</t>
         </is>
       </c>
     </row>
@@ -13708,7 +13708,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Mourning Aix-Tháp Nghịch Cảnh</t>
+          <t>Aix Đau Buồn - Tháp Nghịch Cảnh</t>
         </is>
       </c>
     </row>
@@ -13773,7 +13773,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Mourning Aix-Tháp Nghịch Cảnh</t>
+          <t>Aix Đau Buồn - Tháp Nghịch Cảnh</t>
         </is>
       </c>
     </row>
@@ -13838,7 +13838,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>Mourning Aix-Tô Điểm Lại</t>
+          <t>Aix Đau Buồn - Phác Họa Lại</t>
         </is>
       </c>
     </row>
@@ -13903,7 +13903,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Mourning Aix-Tô Điểm Lại</t>
+          <t>Aix Đau Buồn - Phác Họa Lại</t>
         </is>
       </c>
     </row>
@@ -13968,7 +13968,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Mourning Aix-Kịch</t>
+          <t>Aix Đau Buồn - Bi Kịch</t>
         </is>
       </c>
     </row>
@@ -14033,7 +14033,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Mourning Aix-Kịch</t>
+          <t>Aix Đau Buồn - Bi Kịch</t>
         </is>
       </c>
     </row>
@@ -14098,7 +14098,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Mourning Aix-Võ Đường 1</t>
+          <t>Luyện Tập Mourning Aix - Đạo Trường 1</t>
         </is>
       </c>
     </row>
@@ -14163,7 +14163,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>Mourning Aix-Võ Đường 1</t>
+          <t>Luyện Tập Mourning Aix - Đạo Trường 1</t>
         </is>
       </c>
     </row>
@@ -14228,7 +14228,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Mourning Aix-Võ Đường 2</t>
+          <t>Luyện Tập Mourning Aix - Đạo Trường 2</t>
         </is>
       </c>
     </row>
@@ -14293,7 +14293,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Mourning Aix-Võ Đường 2</t>
+          <t>Luyện Tập Mourning Aix - Đạo Trường 2</t>
         </is>
       </c>
     </row>
@@ -14358,7 +14358,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>Mourning Aix-Võ Đường 3</t>
+          <t>Luyện Tập Mourning Aix - Đạo Trường 3</t>
         </is>
       </c>
     </row>
@@ -14423,7 +14423,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Mourning Aix-Võ Đường 3</t>
+          <t>Luyện Tập Mourning Aix - Đạo Trường 3</t>
         </is>
       </c>
     </row>
@@ -14488,7 +14488,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Mourning Aix-Võ Đường 4</t>
+          <t>Luyện Tập Mourning Aix - Đạo Trường 4</t>
         </is>
       </c>
     </row>
@@ -14553,7 +14553,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Mourning Aix-Võ Đường 4</t>
+          <t>Luyện Tập Mourning Aix - Đạo Trường 4</t>
         </is>
       </c>
     </row>
@@ -14618,7 +14618,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Mourning Aix-Võ Đường 5</t>
+          <t>Luyện Tập Mourning Aix - Đạo Trường 5</t>
         </is>
       </c>
     </row>
@@ -14683,7 +14683,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Mourning Aix-Võ Đường 5</t>
+          <t>Luyện Tập Mourning Aix - Đạo Trường 5</t>
         </is>
       </c>
     </row>
@@ -14748,7 +14748,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Mourning Aix-Võ Đường 6</t>
+          <t>Luyện Tập Mourning Aix - Đạo Trường 6</t>
         </is>
       </c>
     </row>
@@ -14813,7 +14813,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Mourning Aix-Võ Đường 6</t>
+          <t>Luyện Tập Mourning Aix - Đạo Trường 6</t>
         </is>
       </c>
     </row>
@@ -14878,7 +14878,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Tang Lễ Aix - Cấp 65 - Kỹ Thuật Phản Công</t>
+          <t>Aix Tang Tóc - Cấp 65 - Kỹ Thuật Đối Phó</t>
         </is>
       </c>
     </row>
@@ -14943,7 +14943,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Tang Lễ Aix - Cấp 65 - Kỹ Thuật Phản Công</t>
+          <t>Aix Tang Tóc - Cấp 65 - Kỹ Thuật Đối Phó</t>
         </is>
       </c>
     </row>
@@ -15008,7 +15008,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>Mech Abomination - Cấp 55</t>
+          <t>Quái Thú Cơ Khí - Cấp 55</t>
         </is>
       </c>
     </row>
@@ -15073,7 +15073,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Mech Abomination - Cấp 55</t>
+          <t>Quái Thú Cơ Khí - Cấp 55</t>
         </is>
       </c>
     </row>
@@ -15138,7 +15138,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Mech Abomination - Cấp 65</t>
+          <t>Quái Thú Cơ Khí - Cấp 65</t>
         </is>
       </c>
     </row>
@@ -15203,7 +15203,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Mech Abomination - Cấp 65</t>
+          <t>Quái Thú Cơ Khí - Cấp 65</t>
         </is>
       </c>
     </row>
@@ -15268,7 +15268,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Mech Abomination - Cấp 70</t>
+          <t>Quái Thú Cơ Khí - Cấp 70</t>
         </is>
       </c>
     </row>
@@ -15333,7 +15333,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Mech Abomination - Cấp 70</t>
+          <t>Quái Thú Cơ Khí - Cấp 70</t>
         </is>
       </c>
     </row>
@@ -15398,7 +15398,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Impermanence Heron - Cấp 55</t>
+          <t>Diệc Vô Thường - Cấp 55</t>
         </is>
       </c>
     </row>
@@ -15463,7 +15463,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Impermanence Heron - Cấp 55</t>
+          <t>Diệc Vô Thường - Cấp 55</t>
         </is>
       </c>
     </row>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Impermanence Heron - Hạng 65</t>
+          <t>Diệc Vô Thường - Cấp 65</t>
         </is>
       </c>
     </row>
@@ -15593,7 +15593,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Impermanence Heron - Hạng 65</t>
+          <t>Diệc Vô Thường - Cấp 65</t>
         </is>
       </c>
     </row>
@@ -15658,7 +15658,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Impermanence Heron - cấp 70</t>
+          <t>Heron Vô Thường - Cấp 70</t>
         </is>
       </c>
     </row>
@@ -15723,7 +15723,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Impermanence Heron - cấp 70</t>
+          <t>Heron Vô Thường - Cấp 70</t>
         </is>
       </c>
     </row>
@@ -15788,7 +15788,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>Vô Thường Hạc - Cấp 65 - Kỹ Thuật Phản Công</t>
+          <t>Heron Vô Thường - Kỹ Thuật Phản Công - Cấp 65</t>
         </is>
       </c>
     </row>
@@ -15853,7 +15853,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Vô Thường Hạc - Cấp 65 - Kỹ Thuật Phản Công</t>
+          <t>Heron Vô Thường - Kỹ Thuật Phản Công - Cấp 65</t>
         </is>
       </c>
     </row>
@@ -16308,7 +16308,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>TD - Thử nghiệm Missions</t>
+          <t>TD - Kiểm tra nhiệm vụ</t>
         </is>
       </c>
     </row>
@@ -16373,7 +16373,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Sẹo - Pha II - Cấp 55</t>
+          <t>Vết Sẹo - Pha II - Cấp 55</t>
         </is>
       </c>
     </row>
@@ -16438,7 +16438,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Sẹo - Pha II - Cấp 55</t>
+          <t>Vết Sẹo - Pha II - Cấp 55</t>
         </is>
       </c>
     </row>
@@ -16503,7 +16503,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>Sẹo - Pha II - Cấp 65</t>
+          <t>Vết Sẹo - Pha II - Cấp 65</t>
         </is>
       </c>
     </row>
@@ -16568,7 +16568,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>Sẹo - Pha II - Cấp 65</t>
+          <t>Vết Sẹo - Pha II - Cấp 65</t>
         </is>
       </c>
     </row>
@@ -16633,7 +16633,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>Sẹo - Pha II - Cấp 70</t>
+          <t>Vết Sẹo - Pha II - Cấp 70</t>
         </is>
       </c>
     </row>
@@ -16698,7 +16698,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Sẹo - Pha II - Cấp 70</t>
+          <t>Vết Sẹo - Pha II - Cấp 70</t>
         </is>
       </c>
     </row>
@@ -16763,7 +16763,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>Bell-Borne Geochelone - Cấp 55</t>
+          <t>Cấp độ 55 - Rùa Địa Chất Bell-Borne</t>
         </is>
       </c>
     </row>
@@ -16828,7 +16828,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>Bell-Borne Geochelone - Cấp 55</t>
+          <t>Cấp độ 55 - Rùa Địa Chất Bell-Borne</t>
         </is>
       </c>
     </row>
@@ -16893,7 +16893,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>Bell-Borne Geochelone - Hạng 65</t>
+          <t>Rùa Địa Chuông - Cấp 65</t>
         </is>
       </c>
     </row>
@@ -16958,7 +16958,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>Bell-Borne Geochelone - Hạng 65</t>
+          <t>Rùa Địa Chuông - Cấp 65</t>
         </is>
       </c>
     </row>
@@ -17023,7 +17023,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>Bell-Borne Geochelone - Cấp 70</t>
+          <t>Cấp độ 70 - Rùa Địa Chất Bell-Borne</t>
         </is>
       </c>
     </row>
@@ -17088,7 +17088,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>Bell-Borne Geochelone - Cấp 70</t>
+          <t>Cấp độ 70 - Rùa Địa Chất Bell-Borne</t>
         </is>
       </c>
     </row>
@@ -17153,7 +17153,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>Undelusionals - Cấp 55</t>
+          <t>Ảo Tưởng - Cấp 55</t>
         </is>
       </c>
     </row>
@@ -17218,7 +17218,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Undelusionals - Cấp 55</t>
+          <t>Ảo Tưởng - Cấp 55</t>
         </is>
       </c>
     </row>
@@ -17283,7 +17283,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>Undelusionals - Cấp 65</t>
+          <t>Ảo Tưởng - Cấp 65</t>
         </is>
       </c>
     </row>
@@ -17348,7 +17348,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>Undelusionals - Cấp 65</t>
+          <t>Ảo Tưởng - Cấp 65</t>
         </is>
       </c>
     </row>
@@ -17413,7 +17413,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Undelusionals - Cấp 70</t>
+          <t>Ảo Tưởng - Cấp 70</t>
         </is>
       </c>
     </row>
@@ -17478,7 +17478,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Undelusionals - Cấp 70</t>
+          <t>Ảo Tưởng - Cấp 70</t>
         </is>
       </c>
     </row>
@@ -17543,7 +17543,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>Map Kiểm Tra QA</t>
+          <t>Bản Đồ Kiểm Tra QA</t>
         </is>
       </c>
     </row>
@@ -17608,7 +17608,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>Map Thử Nghiệm Bay Lượn</t>
+          <t>Bản Đồ Thử Nghiệm Bay Lơ Lửng</t>
         </is>
       </c>
     </row>
@@ -17673,7 +17673,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>TD - Bản thử nghiệm Quái vật</t>
+          <t>TD - Kiểm tra quái vật</t>
         </is>
       </c>
     </row>
@@ -17738,7 +17738,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Map Test Chuyển động</t>
+          <t>Bản đồ thử nghiệm chuyển động</t>
         </is>
       </c>
     </row>
@@ -17803,7 +17803,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>Map Thử Nghiệm Lối chơi</t>
+          <t>Bản Đồ Thử Nghiệm Gameplay</t>
         </is>
       </c>
     </row>
@@ -17868,7 +17868,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Crownless - Lv. 40</t>
+          <t>Crownless - Cấp 40</t>
         </is>
       </c>
     </row>
@@ -17933,7 +17933,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>Crownless - Lv. 40</t>
+          <t>Crownless - Cấp 40</t>
         </is>
       </c>
     </row>
@@ -18128,7 +18128,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Tempest Mephis I - Cấp 40</t>
+          <t>Mephis Bão Tố I - Cấp 40</t>
         </is>
       </c>
     </row>
@@ -18193,7 +18193,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Tempest Mephis I - Cấp 40</t>
+          <t>Mephis Bão Tố I - Cấp 40</t>
         </is>
       </c>
     </row>
@@ -18258,7 +18258,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>Tempest Mephis I - Cấp 60</t>
+          <t>Mephis Bão Tố I - Cấp 60</t>
         </is>
       </c>
     </row>
@@ -18323,7 +18323,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>Tempest Mephis I - Cấp 60</t>
+          <t>Mephis Bão Tố I - Cấp 60</t>
         </is>
       </c>
     </row>
@@ -18388,7 +18388,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Tempest Mephis II - Cấp 40</t>
+          <t>Mephis Bão Tố II - Cấp 40</t>
         </is>
       </c>
     </row>
@@ -18453,7 +18453,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>Tempest Mephis II - Cấp 40</t>
+          <t>Mephis Bão Tố II - Cấp 40</t>
         </is>
       </c>
     </row>
@@ -18518,7 +18518,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>Tempest Mephis II - Lv. 60</t>
+          <t>Mephis Bão Tố II - Cấp 60</t>
         </is>
       </c>
     </row>
@@ -18583,7 +18583,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>Tempest Mephis II - Lv. 60</t>
+          <t>Mephis Bão Tố II - Cấp 60</t>
         </is>
       </c>
     </row>
@@ -18648,7 +18648,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>Inferno Rider - Lv. 40</t>
+          <t>Kỵ Sĩ Hỏa Ngục - Cấp 40</t>
         </is>
       </c>
     </row>
@@ -18713,7 +18713,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Inferno Rider - Lv. 40</t>
+          <t>Kỵ Sĩ Hỏa Ngục - Cấp 40</t>
         </is>
       </c>
     </row>
@@ -18778,7 +18778,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>Inferno Rider - Lv. 60</t>
+          <t>Kỵ Sĩ Hỏa Ngục - Cấp 60</t>
         </is>
       </c>
     </row>
@@ -18843,7 +18843,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>Inferno Rider - Lv. 60</t>
+          <t>Kỵ Sĩ Hỏa Ngục - Cấp 60</t>
         </is>
       </c>
     </row>
@@ -18908,7 +18908,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>Feilian Beringal - Lv. 40</t>
+          <t>Feilian Beringal - Cấp 40</t>
         </is>
       </c>
     </row>
@@ -18973,7 +18973,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Feilian Beringal - Lv. 40</t>
+          <t>Feilian Beringal - Cấp 40</t>
         </is>
       </c>
     </row>
@@ -19298,7 +19298,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>Lampylumen Myriad - Cấp 60</t>
+          <t>Lampylumen Myriad - Lv. 60</t>
         </is>
       </c>
     </row>
@@ -19363,7 +19363,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Lampylumen Myriad - Cấp 60</t>
+          <t>Lampylumen Myriad - Lv. 60</t>
         </is>
       </c>
     </row>
@@ -19428,7 +19428,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Mourning Aix - Lv. 40</t>
+          <t>Aix Tang Tóc - Cấp 40</t>
         </is>
       </c>
     </row>
@@ -19493,7 +19493,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Mourning Aix - Lv. 40</t>
+          <t>Aix Tang Tóc - Cấp 40</t>
         </is>
       </c>
     </row>
@@ -19688,7 +19688,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>Mech Abomination - Lv. 40</t>
+          <t>Quái Thú Cơ Khí - Cấp 40</t>
         </is>
       </c>
     </row>
@@ -19753,7 +19753,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Mech Abomination - Lv. 40</t>
+          <t>Quái Thú Cơ Khí - Cấp 40</t>
         </is>
       </c>
     </row>
@@ -19818,7 +19818,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Mech Abomination - Cấp 60</t>
+          <t>Quái Thú Cơ Khí - Cấp 60</t>
         </is>
       </c>
     </row>
@@ -19883,7 +19883,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Mech Abomination - Cấp 60</t>
+          <t>Quái Thú Cơ Khí - Cấp 60</t>
         </is>
       </c>
     </row>
@@ -19948,7 +19948,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>Impermanence Heron - Lv. 40</t>
+          <t>Heron Vô Thường - Cấp 40</t>
         </is>
       </c>
     </row>
@@ -20013,7 +20013,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>Impermanence Heron - Lv. 40</t>
+          <t>Heron Vô Thường - Cấp 40</t>
         </is>
       </c>
     </row>
@@ -20078,7 +20078,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Impermanence Heron - Cấp 60</t>
+          <t>Heron Vô Thường - Cấp 60</t>
         </is>
       </c>
     </row>
@@ -20143,7 +20143,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Impermanence Heron - Cấp 60</t>
+          <t>Heron Vô Thường - Cấp 60</t>
         </is>
       </c>
     </row>
@@ -20208,7 +20208,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Scar - Lv. 40</t>
+          <t>Vết Sẹo - Cấp 40</t>
         </is>
       </c>
     </row>
@@ -20273,7 +20273,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Scar - Lv. 40</t>
+          <t>Vết Sẹo - Cấp 40</t>
         </is>
       </c>
     </row>
@@ -20338,7 +20338,7 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>Scar - Cấp 60</t>
+          <t>Vết Sẹo - Cấp 60</t>
         </is>
       </c>
     </row>
@@ -20403,7 +20403,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Scar - Cấp 60</t>
+          <t>Vết Sẹo - Cấp 60</t>
         </is>
       </c>
     </row>
@@ -20468,7 +20468,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Sẹo: Stage II - Cấp 40</t>
+          <t>Scar: Giai Đoạn II - Cấp 40</t>
         </is>
       </c>
     </row>
@@ -20533,7 +20533,7 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Sẹo: Stage II - Cấp 40</t>
+          <t>Scar: Giai Đoạn II - Cấp 40</t>
         </is>
       </c>
     </row>
@@ -20598,7 +20598,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Sẹo: Giai đoạn II - Cấp 60</t>
+          <t>Scar: Giai Đoạn II - Cấp 60</t>
         </is>
       </c>
     </row>
@@ -20663,7 +20663,7 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>Sẹo: Giai đoạn II - Cấp 60</t>
+          <t>Scar: Giai Đoạn II - Cấp 60</t>
         </is>
       </c>
     </row>
@@ -20728,7 +20728,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Bell-Borne Geochelone - Lv. 40</t>
+          <t>Rùa Địa Chuông - Lv. 40</t>
         </is>
       </c>
     </row>
@@ -20793,7 +20793,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Bell-Borne Geochelone - Lv. 40</t>
+          <t>Rùa Địa Chuông - Lv. 40</t>
         </is>
       </c>
     </row>
@@ -20858,7 +20858,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Bell-Borne Geochelone - Lv. 60</t>
+          <t>Rùa Địa Chuông - Lv. 60</t>
         </is>
       </c>
     </row>
@@ -20923,7 +20923,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>Bell-Borne Geochelone - Lv. 60</t>
+          <t>Rùa Địa Chuông - Lv. 60</t>
         </is>
       </c>
     </row>
@@ -20988,7 +20988,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Crownless - True - Lv. 40</t>
+          <t>Crownless - Bản Chính - Cấp 40</t>
         </is>
       </c>
     </row>
@@ -21053,7 +21053,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>Crownless - True - Lv. 40</t>
+          <t>Crownless - Bản Chính - Cấp 40</t>
         </is>
       </c>
     </row>
@@ -21118,7 +21118,7 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>Crownless - Chân - Lv. 60</t>
+          <t>Crownless - Bản Chính - Cấp 60</t>
         </is>
       </c>
     </row>
@@ -21183,7 +21183,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>Crownless - Chân - Lv. 60</t>
+          <t>Crownless - Bản Chính - Cấp 60</t>
         </is>
       </c>
     </row>
@@ -21248,7 +21248,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>Crownless - Chân - Lv. 60</t>
+          <t>Crownless - Bản Chính - Cấp 60</t>
         </is>
       </c>
     </row>
@@ -21313,7 +21313,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>Crownless - Chân - Lv. 60</t>
+          <t>Crownless - Bản Chính - Cấp 60</t>
         </is>
       </c>
     </row>
@@ -21378,7 +21378,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>An'ke Missions Resonance Record Kiểm tra</t>
+          <t>Bản Ghi Cộng Hưởng Nhiệm Vụ An'ke (Thử Nghiệm)</t>
         </is>
       </c>
     </row>
@@ -21443,7 +21443,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>Map Thử Nghiệm - Cao nguyên (Combat)</t>
+          <t>Bản Đồ Thử Nghiệm Chiến Đấu - Cao Nguyên</t>
         </is>
       </c>
     </row>
@@ -21508,7 +21508,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Combat - Map Kiểm Tra Quang Bằng</t>
+          <t>Bản đồ thử nghiệm Chiến đấu - Guan Yaopeng</t>
         </is>
       </c>
     </row>
@@ -21573,7 +21573,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>Map thử nghiệm Combat - Hồ Thanh Lâm</t>
+          <t>Bản đồ thử nghiệm Chiến đấu - Hu Qinglin</t>
         </is>
       </c>
     </row>
@@ -21638,7 +21638,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>Map Thử Nghiệm Combat-金兆文</t>
+          <t>Bản Đồ Thử Nghiệm Chiến Đấu - Kim Triệu Văn</t>
         </is>
       </c>
     </row>
@@ -21703,7 +21703,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Map Thử Nghiệm - Lý Thượng Viễn</t>
+          <t>Bản đồ thử nghiệm Chiến đấu - Li Shangyuan</t>
         </is>
       </c>
     </row>
@@ -21768,7 +21768,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Map Thử Nghiệm - Lý Chính Huy</t>
+          <t>Bản đồ thử nghiệm Chiến đấu - Li Zhenghui</t>
         </is>
       </c>
     </row>
@@ -21833,7 +21833,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>Map Thử Nghiệm Combat-苗家玮</t>
+          <t>Bản đồ thử nghiệm Chiến đấu - Miao Jiawei</t>
         </is>
       </c>
     </row>
@@ -21898,7 +21898,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>Bản Đồ Thử Nghiệm Chiến Đấu-Ninh Bá</t>
+          <t>Bản đồ thử nghiệm Chiến đấu - Ning Bo</t>
         </is>
       </c>
     </row>
@@ -21963,7 +21963,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Map Thử Nghiệm Combat - 宁志同</t>
+          <t>Bản đồ thử nghiệm Chiến đấu - Ning Zhitong</t>
         </is>
       </c>
     </row>
@@ -22028,7 +22028,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>Combat-帅雨阳 Map Thử Nghiệm</t>
+          <t>Bản đồ thử nghiệm Chiến đấu - Shuai Yuyang</t>
         </is>
       </c>
     </row>
@@ -22093,7 +22093,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>Chiến đấu Quách Tử Khang thử nghiệm</t>
+          <t>Thử nghiệm chiến đấu Quách Tử Khang</t>
         </is>
       </c>
     </row>
@@ -22158,7 +22158,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>Chiến Đấu Ngô Nhuận Đông (Test)</t>
+          <t>Thử nghiệm chiến đấu Ngô Nhuận Đông</t>
         </is>
       </c>
     </row>
@@ -22223,7 +22223,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>Chiến đấu Ngô Nghị Tuấn thử nghiệm</t>
+          <t>Thử Nghiệm Chiến Đấu Ngô Nghi Tuấn</t>
         </is>
       </c>
     </row>
@@ -22288,7 +22288,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>Thử Nghiệm Tài Nguyên Chiến Đấu</t>
+          <t>Thử nghiệm Tài Nguyên Chiến Đấu</t>
         </is>
       </c>
     </row>
@@ -22353,7 +22353,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>Kiểm tra nhóm quái</t>
+          <t>Thử Nghiệm Tổ Hợp Quái Vật</t>
         </is>
       </c>
     </row>
@@ -22418,7 +22418,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>Chiến Đấu Đường Cầu Kiểm Tra</t>
+          <t>Thử nghiệm chiến đấu Đường Kiều</t>
         </is>
       </c>
     </row>
@@ -22483,7 +22483,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>Chiến Đấu - Kiểm Tra Thành Danh</t>
+          <t>Thử nghiệm chiến đấu Mã Thành Danh</t>
         </is>
       </c>
     </row>
@@ -22548,7 +22548,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>Bản Đồ Thử Nghiệm Toàn Quái Vật</t>
+          <t>Bản đồ thử nghiệm toàn quái vật</t>
         </is>
       </c>
     </row>
@@ -22678,7 +22678,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>Jinzhou là nơi đặt một trong những trung tâm cơ sở dữ liệu độc đáo của Huanglong, được quản lý bởi Sentinel và kiểm soát bởi Quan Phủ Jinzhou. Nó sử dụng thời gian làm chỉ mục và ghi chép chính xác các thông tin liên quan đến việc thành lập thành phố, tạo nên một nguồn tài nguyên toàn diện và khách quan. Những cuốn sách lớp của Jinzhou, được lưu trữ tại Tòa Thị Chính, chứa đựng dữ liệu quan trọng được thu thập từ thời xa xưa. Cơ sở dữ liệu khổng lồ này chứa đựng câu trả lời cho bất kỳ câu hỏi nào về lịch sử của Huanglong.</t>
+          <t>Tấn Châu là nơi lưu giữ một trong những trung tâm dữ liệu độc đáo của Huanglong, do Sentinel quản lý và dưới sự kiểm soát của Tri phủ Tấn Châu. Hệ thống này lấy thời gian làm chỉ mục và ghi chép chính xác mọi thông tin liên quan đến sự hình thành của thành phố, tạo nên một nguồn tài nguyên toàn diện và khách quan. Những cuốn sách lớp của Tấn Châu, được lưu trữ tại Tòa Thị chính, chứa đựng dữ liệu quan trọng được thu thập từ thời xa xưa. Kho dữ liệu khổng lồ này ẩn chứa câu trả lời cho mọi thắc mắc về lịch sử Huanglong.</t>
         </is>
       </c>
     </row>
@@ -22743,7 +22743,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Thư viện Hoàng Gia</t>
+          <t>Thư Viện Hoàng Gia</t>
         </is>
       </c>
     </row>
@@ -22808,7 +22808,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>Kết hợp nhiều tần số khác nhau, hòa tấu giai điệu chiến đấu.</t>
+          <t>Hòa quyện các tần số, dàn nhạc của những giai điệu chiến trận.</t>
         </is>
       </c>
     </row>
@@ -22873,7 +22873,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>Hiệu ứng Concerto: Hòa Tấu</t>
+          <t>Hiệu Ứng Giao Hưởng: Hòa Tấu</t>
         </is>
       </c>
     </row>
@@ -22938,7 +22938,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>Kết hợp nhiều tần số khác nhau, hòa tấu giai điệu chiến đấu.</t>
+          <t>Hòa quyện các tần số, dàn nhạc của những giai điệu chiến trận.</t>
         </is>
       </c>
     </row>
@@ -23003,7 +23003,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>Hiệu ứng Concerto: Hòa Tấu</t>
+          <t>Hiệu Ứng Giao Hưởng: Hòa Tấu</t>
         </is>
       </c>
     </row>
@@ -23068,7 +23068,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>Các nhạc công hòa tấu hoàn hảo, nhạc cụ hòa quyện tạo nên giai điệu mạnh mẽ và xúc động.</t>
+          <t>Các nhạc công hòa tấu hoàn hảo, nhạc cụ hòa quyện tạo nên một giai điệu mạnh mẽ và lay động lòng người.</t>
         </is>
       </c>
     </row>
@@ -23133,7 +23133,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>Concerto Effect: Đồng Điệu</t>
+          <t>Hiệu Ứng Giao Hưởng: Đồng Thanh</t>
         </is>
       </c>
     </row>
@@ -23198,7 +23198,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>Hủy diệt không phải là phân tán, mà là tạo ra những giai điệu liên tục từ những nốt nhạc mong manh nhất.</t>
+          <t>Hủy diệt không phải là tan biến, mà là tạo nên những giai điệu bất tận từ những nốt nhạc mong manh nhất.</t>
         </is>
       </c>
     </row>
@@ -23263,7 +23263,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>Hiệu Ứng Concerto: Legato</t>
+          <t>Hiệu Ứng Giao Hưởng: Liên Tiết</t>
         </is>
       </c>
     </row>
@@ -23328,7 +23328,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Giai điệu ánh sáng sẽ chế ngự mọi âm thanh bất hòa.</t>
+          <t>Giai điệu ánh sáng sẽ chế ngự mọi âm thanh hỗn loạn.</t>
         </is>
       </c>
     </row>
@@ -23393,7 +23393,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Hiệu Ứng Concerto: Sustenance</t>
+          <t>Hiệu Ứng Giao Hưởng: Duy Trì</t>
         </is>
       </c>
     </row>
@@ -23523,7 +23523,7 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>Dodge</t>
+          <t>Né tránh</t>
         </is>
       </c>
     </row>
@@ -23588,7 +23588,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>Counterattack</t>
+          <t>Phản công</t>
         </is>
       </c>
     </row>
@@ -23718,7 +23718,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>Khi đứng trên mảnh đất của SOL-3, bạn được bao quanh bởi những câu chuyện và huyền thoại về quá khứ của nó, trong khi tương lai đang trải dài dưới chân bạn. Trong ánh sáng vô tận này, vô vàn khả năng đang chờ đợi. Nếu bạn chọn tham gia, có thể bạn sẽ tìm thấy câu trả lời cuối cùng. Nhưng đó không phải là giải pháp đến từ bên ngoài; mà nằm sâu trong quá khứ, tiềm năng vô hạn của tương lai, và chính trái tim bạn.</t>
+          <t>Khi đứng trên mảnh đất SOL-3 này, cậu như được bao bọc bởi những huyền thoại và câu chuyện của quá khứ, trong khi tương lai lại trải dài ngay dưới chân. Trong ánh sáng vô tận này, vô vàn khả năng đang chờ đợi. Nếu cậu chọn bước vào, có lẽ cậu sẽ tìm thấy câu trả lời cuối cùng. Nhưng đó không phải là lời giải đến từ bên ngoài, mà nằm sâu trong quá khứ, trong tiềm năng vô hạn của tương lai, và ngay trong trái tim của chính cậu.</t>
         </is>
       </c>
     </row>
@@ -23783,7 +23783,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>Giai Đoạn Thăng Hoa: I</t>
+          <t>Thăng Hoa Giai Đoạn: I</t>
         </is>
       </c>
     </row>
@@ -23848,7 +23848,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>Giai Đoạn Thăng Hoa: II</t>
+          <t>Thăng Hoa Giai Đoạn: II</t>
         </is>
       </c>
     </row>
@@ -23913,7 +23913,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Giai Đoạn Thăng Hoa: III</t>
+          <t>Thăng Hoa Giai Đoạn: III</t>
         </is>
       </c>
     </row>
@@ -23978,7 +23978,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>Vượt qua thử thách của Sonoro Sphere nhân tạo này để nhận vật phẩm tăng cường Nhân vật.</t>
+          <t>Vượt qua thử thách của Sonoro Sphere nhân tạo này để nhận vật phẩm tăng cường Nhân Vật.</t>
         </is>
       </c>
     </row>
@@ -24043,7 +24043,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>Thuốc Cộng Hưởng</t>
+          <t>Thuốc Tăng Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -24108,7 +24108,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>&lt;color=Ice&gt;Glacio DMG&lt;/color&gt; Bonus tăng 40%.</t>
+          <t>Tăng &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt; thêm 40%.</t>
         </is>
       </c>
     </row>
@@ -24173,7 +24173,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>Vượt qua thử thách trong Sonoro Sphere nhân tạo này để nhận vật phẩm tăng cường Weapon.</t>
+          <t>Vượt qua thử thách của Tổ Tacet nhân tạo này để nhận vật phẩm tăng cường Vũ khí.</t>
         </is>
       </c>
     </row>
@@ -24238,7 +24238,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>Core Năng lượng</t>
+          <t>Lõi Năng Lượng</t>
         </is>
       </c>
     </row>
@@ -24303,7 +24303,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>&lt;color=Fire&gt;Fusion DMG&lt;/color&gt; Bonus tăng 40%.</t>
+          <t>&lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt; tăng thêm 40%.</t>
         </is>
       </c>
     </row>
@@ -24433,7 +24433,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Ống Đã Niêm Phong</t>
+          <t>Ống Niêm Phong</t>
         </is>
       </c>
     </row>
@@ -24498,7 +24498,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>&lt;color=Wind&gt;Aero DMG Bonus&lt;/color&gt; thêm 40%.</t>
+          <t>Tỷ lệ &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt; tăng thêm 40%.</t>
         </is>
       </c>
     </row>
@@ -24563,7 +24563,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>Vượt qua thử thách của Sonoro Sphere nhân tạo này để nhận được những tài nguyên không thể thiếu.</t>
+          <t>Vượt qua thử thách của Tổ Tacet nhân tạo này để nhận những tài nguyên không thể thiếu.</t>
         </is>
       </c>
     </row>
@@ -24693,7 +24693,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>&lt;color=Thunder&gt;Electro DMG&lt;/color&gt; Bonus tăng 40%.</t>
+          <t>&lt;color=Thunder&gt;Tăng 40% Sát Thương Điện&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -24758,7 +24758,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>POS测试副本</t>
+          <t>PHÓ BẢN KIỂM TRA POS</t>
         </is>
       </c>
     </row>
@@ -24823,7 +24823,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>TD-Action测试</t>
+          <t>Kiểm tra Hành động TD</t>
         </is>
       </c>
     </row>
@@ -24888,7 +24888,7 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>TD-Flow测试</t>
+          <t>Kiểm tra Luồng TD</t>
         </is>
       </c>
     </row>
@@ -24953,7 +24953,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>TD-Component Test</t>
+          <t>Kiểm tra mô-đun TD</t>
         </is>
       </c>
     </row>
@@ -25018,7 +25018,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>TD-Kiểm Tra Cơ Cấu</t>
+          <t>Kiểm tra cơ quan TD</t>
         </is>
       </c>
     </row>
@@ -25083,7 +25083,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>TD-Bản thử nghiệm</t>
+          <t>Kiểm tra phụ bản TD</t>
         </is>
       </c>
     </row>
@@ -25148,7 +25148,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Missions An'ke 人形 Cô gái trẻ 房间</t>
+          <t>nhiệm vụ thử nghiệm An'ke - Búp bê - Cô bé - Phòng</t>
         </is>
       </c>
     </row>
@@ -25213,7 +25213,7 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>Biên Bản Cộng Hưởng Nhiệm Vụ An'ke Chính Thức</t>
+          <t>Bản Ghi Cộng Hưởng Nhiệm Vụ An'ke Chính Thức</t>
         </is>
       </c>
     </row>
@@ -25279,7 +25279,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Jinzhou là nơi đặt một trong những trung tâm cơ sở dữ liệu độc đáo của Huanglong, được quản lý bởi Sentinel và kiểm soát bởi Tri Châu Jinzhou. Nó sử dụng thời gian làm chỉ mục và ghi chép chính xác các thông tin liên quan đến quá trình thành lập thành phố, biến nó thành một nguồn tài nguyên toàn diện và khách quan. Các bộ sách giáo khoa của Jinzhou, được lưu trữ tại Tòa Thị Chính, chứa đựng những dữ liệu quan trọng được thu thập từ thời xa xưa. Cơ sở dữ liệu khổng lồ này chứa đựng câu trả lời cho bất kỳ câu hỏi nào về lịch sử của Huanglong.
+          <t>Tấn Châu là nơi lưu giữ một trong những trung tâm dữ liệu độc đáo của Huanglong, do Sentinel quản lý và dưới sự kiểm soát của Tri phủ Tấn Châu. Hệ thống này lấy thời gian làm chỉ mục và ghi chép chính xác mọi thông tin liên quan đến sự hình thành của thành phố, tạo nên một nguồn tài nguyên toàn diện và khách quan. Những cuốn sách lớp của Tấn Châu, được lưu trữ tại Tòa Thị chính, chứa đựng dữ liệu quan trọng được thu thập từ thời xa xưa. Kho dữ liệu khổng lồ này ẩn chứa câu trả lời cho mọi thắc mắc về lịch sử Huanglong.
 &lt;color=HighlightB&gt;Cấp độ nhân vật đề xuất: Cấp 40&lt;/color&gt;</t>
         </is>
       </c>
@@ -25345,7 +25345,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Thư viện Hoàng Gia</t>
+          <t>Thư Viện Hoàng Gia</t>
         </is>
       </c>
     </row>
@@ -25410,7 +25410,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>Thử Nghiệm CE Chiến Đấu Yangyang</t>
+          <t>Thử nghiệm Chiến Đấu CE của Yangyang</t>
         </is>
       </c>
     </row>
@@ -25475,7 +25475,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>Cơ Giới Biến Dị CE</t>
+          <t>Biến thể Cơ khí CE</t>
         </is>
       </c>
     </row>
@@ -25540,7 +25540,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>Tầng 2 Tháp</t>
+          <t>Tầng thứ hai của Tháp</t>
         </is>
       </c>
     </row>
@@ -25605,7 +25605,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>Có người có thể phủ nhận tất cả là giả dối, nhưng kẻ khôn ngoan thật sự có thể nhận ra chân lý ngay cả trong sự lừa dối. Khái niệm này cũng áp dụng cho huấn luyện ảo.</t>
+          <t>Có kẻ coi mọi thứ đều là giả dối, nhưng người thực sự thông thái vẫn nhận ra chân lý ngay cả trong sự lừa gạt. Khái niệm này cũng áp dụng cho huấn luyện ảo.</t>
         </is>
       </c>
     </row>
@@ -25670,7 +25670,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>Máy Huấn Luyện - Yangyang</t>
+          <t>Mô phỏng huấn luyện - Yangyang</t>
         </is>
       </c>
     </row>
@@ -25735,7 +25735,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Máy Huấn Luyện - Chixia</t>
+          <t>Mô phỏng huấn luyện - Chixia</t>
         </is>
       </c>
     </row>
@@ -25800,7 +25800,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>Máy Huấn Luyện - Camellya</t>
+          <t>Máy Chiếu Huấn Luyện - Camellya</t>
         </is>
       </c>
     </row>
@@ -25865,7 +25865,7 @@
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>Máy Huấn Luyện - Rover (Nam)</t>
+          <t>Mô phỏng huấn luyện - Rover (Nam)</t>
         </is>
       </c>
     </row>
@@ -25930,7 +25930,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>Máy Huấn Luyện - Rover (Nữ)</t>
+          <t>Mô phỏng huấn luyện - Rover (Nữ)</t>
         </is>
       </c>
     </row>
@@ -25995,7 +25995,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>Máy Huấn Luyện - Taoqi</t>
+          <t>Mô phỏng huấn luyện - Taoqi</t>
         </is>
       </c>
     </row>
@@ -26060,7 +26060,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Máy Huấn Luyện - Verina</t>
+          <t>Mô phỏng huấn luyện - Verina</t>
         </is>
       </c>
     </row>
@@ -26125,7 +26125,7 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>Máy Huấn Luyện - Sanhua</t>
+          <t>Mô phỏng huấn luyện - Sanhua</t>
         </is>
       </c>
     </row>
@@ -26190,7 +26190,7 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>Máy Huấn Luyện - Baizhi</t>
+          <t>Máy Chiếu Huấn Luyện - Baizhi</t>
         </is>
       </c>
     </row>
@@ -26255,7 +26255,7 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>Máy Huấn Luyện - Encore</t>
+          <t>Mô phỏng huấn luyện - Encore</t>
         </is>
       </c>
     </row>
@@ -26320,7 +26320,7 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>Máy Huấn Luyện - Danjin</t>
+          <t>Mô phỏng huấn luyện - Danjin</t>
         </is>
       </c>
     </row>
@@ -26385,7 +26385,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>Máy Huấn Luyện - Aalto</t>
+          <t>Máy Chiếu Huấn Luyện - Aalto</t>
         </is>
       </c>
     </row>
@@ -26450,7 +26450,7 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>Máy Huấn Luyện - Jiyan</t>
+          <t>Mô phỏng huấn luyện - Jiyan</t>
         </is>
       </c>
     </row>
@@ -26515,7 +26515,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>Máy Huấn Luyện - Mortefi</t>
+          <t>Mô phỏng huấn luyện - Mortefi</t>
         </is>
       </c>
     </row>
@@ -26580,7 +26580,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>Máy Huấn Luyện - Calcharo</t>
+          <t>Máy Chiếu Huấn Luyện - Calcharo</t>
         </is>
       </c>
     </row>
@@ -26645,7 +26645,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>Máy Huấn Luyện - Yinlin</t>
+          <t>Mô phỏng Huấn luyện - Yinlin</t>
         </is>
       </c>
     </row>
@@ -26710,7 +26710,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>Máy Huấn Luyện - Yuanwu</t>
+          <t>Mô phỏng Huấn luyện - Yuanwu</t>
         </is>
       </c>
     </row>
@@ -26775,7 +26775,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>Máy Huấn Luyện - Thử Nghiệm</t>
+          <t>Mô phỏng huấn luyện - Kiểm tra</t>
         </is>
       </c>
     </row>
@@ -26840,7 +26840,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>Thử Nghiệm TD-Levitator</t>
+          <t>Kiểm tra Bộ nâng TD</t>
         </is>
       </c>
     </row>
@@ -26905,7 +26905,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>Ta测试</t>
+          <t>Kiểm tra khiêu khích</t>
         </is>
       </c>
     </row>
@@ -26970,7 +26970,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>Trong hình thức ẩn chứa ý nghĩa cố hữu, một sự thống nhất hài hòa. Trong đồ họa là chân lý của quy tắc và chiều không gian.</t>
+          <t>Trong hình hài, ẩn chứa ý nghĩa, một sự hòa điệu thống nhất. Bên trong những đường nét đồ họa là chân lý của quy luật và chiều không gian.</t>
         </is>
       </c>
     </row>
@@ -27100,7 +27100,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>Dù bị giới hạn trong một chiều duy nhất, trục X, bạn vẫn phải tiếp tục tiến về phía trước theo đúng hướng.</t>
+          <t>Dù bị giới hạn trong một chiều duy nhất, trục X, cậu vẫn phải tiếp tục tiến về phía trước theo đúng hướng.</t>
         </is>
       </c>
     </row>
@@ -27230,7 +27230,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>Thử Nghiệm Phụ Bản Chung</t>
+          <t>Thử nghiệm chung cho Phụ Bản</t>
         </is>
       </c>
     </row>
@@ -27295,7 +27295,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>Một trong những trung tâm cơ sở dữ liệu lớn đặc trưng của Huanglong, do Sentinels và các quan chức địa phương quản lý. Nó sử dụng thời gian làm chỉ mục và ghi chép chính xác thông tin liên quan đến sự hình thành của thành phố, trở thành nguồn tài nguyên toàn diện và khách quan. Những cuốn sách lớp của Jinzhou, được lưu trữ tại City Hall, chứa đựng dữ liệu quan trọng được thu thập từ thời xa xưa. Cơ sở dữ liệu khổng lồ này chứa đựng câu trả lời cho mọi câu hỏi về lịch sử của Huanglong.</t>
+          <t>Một trong những trung tâm cơ sở dữ liệu lớn đặc trưng của Huanglong, do các Sentinel và quan chức địa phương quản lý. Nó sử dụng thời gian làm chỉ mục và ghi chép chính xác mọi thông tin liên quan đến sự hình thành của thành phố, biến nó thành nguồn tài nguyên toàn diện và khách quan. Những cuốn sách cổ của Jinzhou, được lưu trữ tại City Hall, chứa đựng dữ liệu quan trọng được thu thập từ thời xa xưa. Cơ sở dữ liệu khổng lồ này ẩn chứa câu trả lời cho mọi câu hỏi về lịch sử Huanglong.</t>
         </is>
       </c>
     </row>
@@ -27360,7 +27360,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>Thư viện Hoàng Gia</t>
+          <t>Thư Viện Hoàng Gia</t>
         </is>
       </c>
     </row>
@@ -27425,7 +27425,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>Nghiên cứu chuyển cảnh - Tháp leo tầng đơn cảnh</t>
+          <t>Nghiên Cứu Chuyển Cảnh - Tháp Leo Đơn Cảnh</t>
         </is>
       </c>
     </row>
@@ -27490,7 +27490,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>Nghiên cứu chuyển cảnh - Tháp leo tầng 4</t>
+          <t>Nghiên Cứu Chuyển Cảnh - Tháp Leo 4 Cảnh Chuyển Tiếp</t>
         </is>
       </c>
     </row>
@@ -27555,7 +27555,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>Nghiên cứu chuyển cảnh - Đa cảnh</t>
+          <t>Nghiên Cứu Chuyển Cảnh - Đa Cảnh Chuyển Tiếp</t>
         </is>
       </c>
     </row>
@@ -27620,7 +27620,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>Function Bản sao Thử nghiệm</t>
+          <t>Trình diễn chức năng Phụ Bản</t>
         </is>
       </c>
     </row>
@@ -27685,7 +27685,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>Thử Nghiệm Phụ Bản - Hiệp 1 &amp; 2</t>
+          <t>Thử nghiệm副本 - Hiệp đầu và hiệp cuối</t>
         </is>
       </c>
     </row>
@@ -27750,7 +27750,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>Phó Bản Thử Nghiệm - Chế Độ Bảo Vệ</t>
+          <t>Thử nghiệm副本 - Chế độ bảo vệ</t>
         </is>
       </c>
     </row>
@@ -27819,7 +27819,7 @@
         <is>
           <t>Thời lượng: 30 phút
 Sản xuất: SOL-3 Picture Studios
-Tóm tắt: Một cô bé mơ ước trở thành anh hùng, bất ngờ có được sức mạnh biến hình. Liệu ước mơ thời thơ ấu của cô có thành hiện thực?</t>
+Tóm tắt: Một cô bé mơ ước trở thành anh hùng, bất ngờ nhận được sức mạnh biến hình. Liệu ước mơ tuổi thơ của cô có thành hiện thực?</t>
         </is>
       </c>
     </row>
@@ -27952,8 +27952,8 @@
       <c r="M423" t="inlineStr">
         <is>
           <t>Thời lượng: 60 phút
-Sản xuất bởi: Dream Pictures
-Tóm tắt: Ngoài vùng biên giới bị chiến tranh tàn phá, Đỉnh Bất Tử mở cửa trở lại sau chu kỳ mười sáu năm. Các phe phái từ khắp nơi tụ họp, háo hức giành lấy kho báu huyền thoại của nó.</t>
+Sản xuất: Dream Pictures
+Tóm tắt: Ngoài vùng biên giới chiến tranh, Đỉnh Bất Tử mở cửa trở lại sau chu kỳ mười sáu năm. Các thế lực từ khắp nơi đổ về, háo hức chiếm lấy kho báu huyền thoại.</t>
         </is>
       </c>
     </row>
@@ -28018,7 +28018,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>Quán Trọ Mt. Firmament</t>
+          <t>Quán trọ Núi Firmament</t>
         </is>
       </c>
     </row>
@@ -28087,7 +28087,7 @@
         <is>
           <t>Thời lượng: 60 phút
 Sản xuất: Sentry Bros.
-Tóm tắt: Một tên tội phạm thách thức hệ thống phán xét mọi hành vi sai trái: nếu kẻ phạm tội bị bắt trước khi gây án, liệu khái niệm tội phạm còn ý nghĩa?</t>
+Tóm tắt: Một tên tội phạm thách thức hệ thống phán xét mọi lỗi lầm: nếu kẻ phạm tội bị bắt trước khi gây án, liệu tội ác còn ý nghĩa gì?</t>
         </is>
       </c>
     </row>
@@ -28152,7 +28152,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Psyche Pass: Kẻ Nổi Loạn</t>
+          <t>Thẻ Tâm Lý: Kẻ Bất Quy Tắc</t>
         </is>
       </c>
     </row>
@@ -28286,7 +28286,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>Vị Khách Của Ragunna</t>
+          <t>Vị Khách của Ragunna</t>
         </is>
       </c>
     </row>
@@ -28355,7 +28355,7 @@
         <is>
           <t>Thời lượng: 60 phút
 Sản xuất: Somnoire Box Office
-Tóm tắt: Những gì đáng lẽ là đêm bế mạc hoành tráng của Liên hoan Film lại biến thành một "hòn đảo cô lập" sau một sự cố bất ngờ. Khi hung thủ tuyên bố tội ác của mình, một bi kịch được dàn dựng kỹ lưỡng bắt đầu hé lộ...</t>
+Tóm tắt: Buổi bế mạc hoành tráng của Liên hoan Phim bất ngờ biến thành "hòn đảo cô lập" sau một tai nạn đột ngột. Khi thủ phạm tuyên bố tội ác của mình, một bi kịch được dàn dựng kỹ lưỡng bắt đầu hé lộ...</t>
         </is>
       </c>
     </row>
@@ -28420,7 +28420,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Vụ Án Tại Rạp Chiếu Phim</t>
+          <t>Vụ Án Rạp Chiếu Phim</t>
         </is>
       </c>
     </row>
@@ -28485,7 +28485,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Bóng tối u ám nhìn chằm chằm vào bạn bằng đôi mắt rực lửa, như thể muốn kéo bạn trở lại bóng tối vô tận. Hãy bước vào Somnoire cùng những người bạn đáng tin cậy, kết nối tâm trí và tinh thần, và sống lại trận chiến hoành tráng chống lại cơn ác mộng luôn rình rập.</t>
+          <t>Bóng tối đang nhìn ngươi bằng đôi mắt rực lửa, như muốn kéo ngươi trở lại vực thẳm vô tận. Hãy bước vào Somnoire cùng những người đồng hành đáng tin, kết nối tâm trí và tinh thần, tái hiện lại trận chiến huyền thoại chống lại ác mộng luôn rình rập.</t>
         </is>
       </c>
     </row>
@@ -28550,7 +28550,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>Bóng tối u ám nhìn chằm chằm vào bạn bằng đôi mắt rực lửa, như thể muốn kéo bạn trở lại bóng tối vô tận. Hãy bước vào Somnoire cùng những người bạn đáng tin cậy, kết nối tâm trí và tinh thần, và sống lại trận chiến hoành tráng chống lại cơn ác mộng luôn rình rập.</t>
+          <t>Bóng tối đang nhìn ngươi bằng đôi mắt rực lửa, như muốn kéo ngươi trở lại vực thẳm vô tận. Hãy bước vào Somnoire cùng những người đồng hành đáng tin, kết nối tâm trí và tinh thần, tái hiện lại trận chiến huyền thoại chống lại ác mộng luôn rình rập.</t>
         </is>
       </c>
     </row>
@@ -28615,7 +28615,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>Lời Triệu Tập Quỷ Dị II</t>
+          <t>Lời Triệu Hồi U Minh II</t>
         </is>
       </c>
     </row>
@@ -28680,7 +28680,7 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>Bóng tối u ám nhìn chằm chằm vào bạn bằng đôi mắt rực lửa, như thể muốn kéo bạn trở lại bóng tối vô tận. Hãy bước vào Somnoire cùng những người bạn đáng tin cậy, kết nối tâm trí và tinh thần, và sống lại trận chiến hoành tráng chống lại cơn ác mộng luôn rình rập.</t>
+          <t>Bóng tối đang nhìn ngươi bằng đôi mắt rực lửa, như muốn kéo ngươi trở lại vực thẳm vô tận. Hãy bước vào Somnoire cùng những người đồng hành đáng tin, kết nối tâm trí và tinh thần, tái hiện lại trận chiến huyền thoại chống lại ác mộng luôn rình rập.</t>
         </is>
       </c>
     </row>
@@ -28745,7 +28745,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Nỗi Kinh Hoàng Tái Sinh I</t>
+          <t>Hồi Sinh Khủng Bố I</t>
         </is>
       </c>
     </row>
@@ -28810,7 +28810,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>Bóng tối u ám nhìn chằm chằm vào bạn bằng đôi mắt rực lửa, như thể muốn kéo bạn trở lại bóng tối vô tận. Hãy bước vào Somnoire cùng những người bạn đáng tin cậy, kết nối tâm trí và tinh thần, và sống lại trận chiến hoành tráng chống lại cơn ác mộng luôn rình rập.</t>
+          <t>Bóng tối đang nhìn ngươi bằng đôi mắt rực lửa, như muốn kéo ngươi trở lại vực thẳm vô tận. Hãy bước vào Somnoire cùng những người đồng hành đáng tin, kết nối tâm trí và tinh thần, tái hiện lại trận chiến huyền thoại chống lại ác mộng luôn rình rập.</t>
         </is>
       </c>
     </row>
@@ -28875,7 +28875,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Lời Triệu Tập Quỷ Dị III</t>
+          <t>Lời Triệu Hồi U Minh III</t>
         </is>
       </c>
     </row>
@@ -28940,7 +28940,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Bóng tối u ám nhìn chằm chằm vào bạn bằng đôi mắt rực lửa, như thể muốn kéo bạn trở lại bóng tối vô tận. Hãy bước vào Somnoire cùng những người bạn đáng tin cậy, kết nối tâm trí và tinh thần, và sống lại trận chiến hoành tráng chống lại cơn ác mộng luôn rình rập.</t>
+          <t>Bóng tối đang nhìn ngươi bằng đôi mắt rực lửa, như muốn kéo ngươi trở lại vực thẳm vô tận. Hãy bước vào Somnoire cùng những người đồng hành đáng tin, kết nối tâm trí và tinh thần, tái hiện lại trận chiến huyền thoại chống lại ác mộng luôn rình rập.</t>
         </is>
       </c>
     </row>
@@ -29005,7 +29005,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>Lời Triệu Tập Quỷ Dị IV</t>
+          <t>Lời Triệu Hồi U Minh IV</t>
         </is>
       </c>
     </row>
@@ -29070,7 +29070,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>Bóng tối u ám nhìn chằm chằm vào bạn bằng đôi mắt rực lửa, như thể muốn kéo bạn trở lại bóng tối vô tận. Hãy bước vào Somnoire cùng những người bạn đáng tin cậy, kết nối tâm trí và tinh thần, và sống lại trận chiến hoành tráng chống lại cơn ác mộng luôn rình rập.</t>
+          <t>Bóng tối đang nhìn ngươi bằng đôi mắt rực lửa, như muốn kéo ngươi trở lại vực thẳm vô tận. Hãy bước vào Somnoire cùng những người đồng hành đáng tin, kết nối tâm trí và tinh thần, tái hiện lại trận chiến huyền thoại chống lại ác mộng luôn rình rập.</t>
         </is>
       </c>
     </row>
@@ -29135,7 +29135,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>Nỗi Kinh Hoàng Tái Sinh II</t>
+          <t>Hồi Sinh Khủng Bố II</t>
         </is>
       </c>
     </row>
@@ -29265,7 +29265,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>Dungeon Test - Đợt quái</t>
+          <t>Thử nghiệm Bản Đồ - Đợt Quái Tăng Cường</t>
         </is>
       </c>
     </row>
@@ -29330,7 +29330,7 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>Một cánh cổng bí ẩn xuất hiện tại Bãi Lầy Aix Rên Rỉ, mở ra một thế giới gọi là Somnoire. Tương truyền, nơi đây chứa đựng những giấc mơ của tất cả sinh linh ở Solaris.</t>
+          <t>Một cánh cổng bí ẩn hiện ra tại Đầm Than Vãn Aix, mở lối đến cõi Somnoire. Theo truyền thuyết, nơi đây chứa đựng giấc mơ của mọi sinh linh trên Solaris.</t>
         </is>
       </c>
     </row>
@@ -29395,7 +29395,7 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>rogue-Demo</t>
+          <t>Demo-độc hành</t>
         </is>
       </c>
     </row>
@@ -29460,7 +29460,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>Một cánh cổng bí ẩn xuất hiện tại Bãi Lầy Aix Rên Rỉ, mở ra một thế giới gọi là Somnoire. Tương truyền, nơi đây chứa đựng những giấc mơ của tất cả sinh linh ở Solaris.</t>
+          <t>Một cánh cổng bí ẩn hiện ra tại Đầm Than Vãn Aix, mở lối đến cõi Somnoire. Theo truyền thuyết, nơi đây chứa đựng giấc mơ của mọi sinh linh trên Solaris.</t>
         </is>
       </c>
     </row>
@@ -29525,7 +29525,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>Vực Sâu Của Thế Giới Ảo Ảnh I</t>
+          <t>Vực Sâu Cõi Ảo I</t>
         </is>
       </c>
     </row>
@@ -29590,7 +29590,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Một cánh cổng bí ẩn xuất hiện tại Bãi Lầy Aix Rên Rỉ, mở ra một thế giới gọi là Somnoire. Tương truyền, nơi đây chứa đựng những giấc mơ của tất cả sinh linh ở Solaris.</t>
+          <t>Một cánh cổng bí ẩn hiện ra tại Đầm Than Vãn Aix, mở lối đến cõi Somnoire. Theo truyền thuyết, nơi đây chứa đựng giấc mơ của mọi sinh linh trên Solaris.</t>
         </is>
       </c>
     </row>
@@ -29655,7 +29655,7 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>Vực Sâu Của Thế Giới Ảo Ảnh II</t>
+          <t>Vực Sâu Cõi Ảo II</t>
         </is>
       </c>
     </row>
@@ -29720,7 +29720,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Một cánh cổng bí ẩn xuất hiện tại Bãi Lầy Aix Rên Rỉ, mở ra một thế giới gọi là Somnoire. Tương truyền, nơi đây chứa đựng những giấc mơ của tất cả sinh linh ở Solaris.</t>
+          <t>Một cánh cổng bí ẩn hiện ra tại Đầm Than Vãn Aix, mở lối đến cõi Somnoire. Theo truyền thuyết, nơi đây chứa đựng giấc mơ của mọi sinh linh trên Solaris.</t>
         </is>
       </c>
     </row>
@@ -29785,7 +29785,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>Vực Sâu Của Thế Giới Ảo Ảnh III</t>
+          <t>Vực Sâu Cõi Ảo III</t>
         </is>
       </c>
     </row>
@@ -29850,7 +29850,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>Vực Sâu Của Thế Giới Ảo Ảnh IV</t>
+          <t>Tổ Tacet Ảo Ảnh IV</t>
         </is>
       </c>
     </row>
@@ -29915,7 +29915,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Vực Sâu Của Thế Giới Ảo Ảnh V</t>
+          <t>Tổ Tacet Ảo Ảnh V</t>
         </is>
       </c>
     </row>
@@ -30045,7 +30045,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>Vực Sâu Cõi Ảo Ảnh</t>
+          <t>Vực Sâu Cõi Ảo</t>
         </is>
       </c>
     </row>
@@ -30110,7 +30110,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>Bản Thử Nghiệm Nhân Vật Jiyan</t>
+          <t>Bản thử nghiệm nhân vật Jiyan</t>
         </is>
       </c>
     </row>
@@ -30175,7 +30175,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>Bản Sao Trial Character Barr</t>
+          <t>Bản Thử Nghiệm Nhân Vật Barr</t>
         </is>
       </c>
     </row>
@@ -30240,7 +30240,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Bản Thử Nghiệm Nhân Vật Danjin</t>
+          <t>Bản thử nghiệm nhân vật Danjin</t>
         </is>
       </c>
     </row>
@@ -30305,7 +30305,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>Bản Thử Nghiệm Nhân Vật Chixia</t>
+          <t>Bản thử nghiệm nhân vật Chixia</t>
         </is>
       </c>
     </row>
@@ -30370,7 +30370,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>Bản Thử Nghiệm Nhân Vật Yinlin</t>
+          <t>Bản thử nghiệm nhân vật Yinlin</t>
         </is>
       </c>
     </row>
@@ -30435,7 +30435,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>Bản Thử Nghiệm Nhân Vật Taoqi</t>
+          <t>Taoqi: Bản thử nghiệm nhân vật</t>
         </is>
       </c>
     </row>
@@ -30500,7 +30500,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>Bản Thử Nghiệm Nhân Vật Aalto</t>
+          <t>AaltoBản thử nghiệm nhân vật</t>
         </is>
       </c>
     </row>
@@ -30565,7 +30565,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Bản Thử Nghiệm Nhân Vật Yuanwu</t>
+          <t>Yuanwu: Bản thử nghiệm nhân vật</t>
         </is>
       </c>
     </row>
@@ -30630,7 +30630,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>Mộng Ảo Nở Hoa</t>
+          <t>Mộng Ảo Nở Rộ</t>
         </is>
       </c>
     </row>
@@ -30695,7 +30695,7 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>Sân Khấu Của Chiến Binh Nhỏ</t>
+          <t>Sân Khấu Chiến Binh Nhỏ</t>
         </is>
       </c>
     </row>
@@ -30890,7 +30890,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Ngọn Núi Và Sáu Đồng Tín Dụng</t>
+          <t>Ngọn Núi và Sáu Đồng Tín</t>
         </is>
       </c>
     </row>
@@ -30955,7 +30955,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Bất Chấp Mọi Tình Huống</t>
+          <t>Vượt Qua Mọi Gian Nan</t>
         </is>
       </c>
     </row>
@@ -31020,7 +31020,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Một vết nứt bí ẩn đột nhiên xuất hiện sâu trong mỏ. Trong Sonoro Sphere đặc biệt này, những hợp kim do Shilang rèn tạo sẽ mang đến sự trợ giúp bất ngờ cho bạn.</t>
+          <t>Một vết nứt bí ẩn đột nhiên xuất hiện sâu trong mỏ. Trong Sonoro Sphere đặc biệt này, những hợp kim do Shilang rèn tạo lại mang đến sự trợ giúp bất ngờ cho cậu.</t>
         </is>
       </c>
     </row>
@@ -31085,7 +31085,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>Khe Hở Hơi Thở</t>
+          <t>Vết Nứt Hơi Thở</t>
         </is>
       </c>
     </row>
@@ -31150,7 +31150,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Một vết nứt bí ẩn đột nhiên xuất hiện sâu trong mỏ. Trong Sonoro Sphere đặc biệt này, những hợp kim do Shilang rèn tạo sẽ mang đến sự trợ giúp bất ngờ cho bạn.</t>
+          <t>Một vết nứt bí ẩn đột nhiên xuất hiện sâu trong mỏ. Trong Sonoro Sphere đặc biệt này, những hợp kim do Shilang rèn tạo lại mang đến sự trợ giúp bất ngờ cho cậu.</t>
         </is>
       </c>
     </row>
@@ -31280,7 +31280,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Một vết nứt bí ẩn đột nhiên xuất hiện sâu trong mỏ. Trong Sonoro Sphere đặc biệt này, những hợp kim do Shilang rèn tạo sẽ mang đến sự trợ giúp bất ngờ cho bạn.</t>
+          <t>Một vết nứt bí ẩn đột nhiên xuất hiện sâu trong mỏ. Trong Sonoro Sphere đặc biệt này, những hợp kim do Shilang rèn tạo lại mang đến sự trợ giúp bất ngờ cho cậu.</t>
         </is>
       </c>
     </row>
@@ -31345,7 +31345,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Khe Nứt Cháy Bỏng</t>
+          <t>Vết Nứt Nóng Rực</t>
         </is>
       </c>
     </row>
@@ -31410,7 +31410,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>Một vết nứt bí ẩn đột nhiên xuất hiện sâu trong mỏ. Trong Sonoro Sphere đặc biệt này, những hợp kim do Shilang rèn tạo sẽ mang đến sự trợ giúp bất ngờ cho bạn.</t>
+          <t>Một vết nứt bí ẩn đột nhiên xuất hiện sâu trong mỏ. Trong Sonoro Sphere đặc biệt này, những hợp kim do Shilang rèn tạo lại mang đến sự trợ giúp bất ngờ cho cậu.</t>
         </is>
       </c>
     </row>
@@ -31475,7 +31475,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>Khe Nứt Tốc Độ</t>
+          <t>Vết Nứt Rapido</t>
         </is>
       </c>
     </row>
@@ -31540,7 +31540,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>Một vết nứt bí ẩn đột nhiên xuất hiện sâu trong mỏ. Trong Sonoro Sphere đặc biệt này, những hợp kim do Shilang rèn tạo sẽ mang đến sự trợ giúp bất ngờ cho bạn.</t>
+          <t>Một vết nứt bí ẩn đột nhiên xuất hiện sâu trong mỏ. Trong Sonoro Sphere đặc biệt này, những hợp kim do Shilang rèn tạo lại mang đến sự trợ giúp bất ngờ cho cậu.</t>
         </is>
       </c>
     </row>
@@ -31605,7 +31605,7 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>Khe Nứt Công Kích</t>
+          <t>Khe Nứt Đòn Đánh</t>
         </is>
       </c>
     </row>
@@ -31670,7 +31670,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Một vết nứt bí ẩn đột nhiên xuất hiện sâu trong mỏ. Trong Sonoro Sphere đặc biệt này, những hợp kim do Shilang rèn tạo sẽ mang đến sự trợ giúp bất ngờ cho bạn.</t>
+          <t>Một vết nứt bí ẩn đột nhiên xuất hiện sâu trong mỏ. Trong Sonoro Sphere đặc biệt này, những hợp kim do Shilang rèn tạo lại mang đến sự trợ giúp bất ngờ cho cậu.</t>
         </is>
       </c>
     </row>
@@ -31735,7 +31735,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Khe Nứt Uy Hiếp</t>
+          <t>Vết Rạn Uy Hiếp</t>
         </is>
       </c>
     </row>
@@ -31800,7 +31800,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>Một vết nứt bí ẩn đột nhiên xuất hiện sâu trong mỏ. Trong Sonoro Sphere đặc biệt này, những hợp kim do Shilang rèn tạo sẽ mang đến sự trợ giúp bất ngờ cho bạn.</t>
+          <t>Một vết nứt bí ẩn đột nhiên xuất hiện sâu trong mỏ. Trong Sonoro Sphere đặc biệt này, những hợp kim do Shilang rèn tạo lại mang đến sự trợ giúp bất ngờ cho cậu.</t>
         </is>
       </c>
     </row>
@@ -31865,7 +31865,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Khe Nứt Chấn Động</t>
+          <t>Khe Nứt Đinh Tai</t>
         </is>
       </c>
     </row>
@@ -31930,7 +31930,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Một vết nứt bí ẩn đột nhiên xuất hiện sâu trong mỏ. Trong Sonoro Sphere đặc biệt này, những hợp kim do Shilang rèn tạo sẽ mang đến sự trợ giúp bất ngờ cho bạn.</t>
+          <t>Một vết nứt bí ẩn đột nhiên xuất hiện sâu trong mỏ. Trong Sonoro Sphere đặc biệt này, những hợp kim do Shilang rèn tạo lại mang đến sự trợ giúp bất ngờ cho cậu.</t>
         </is>
       </c>
     </row>
@@ -32060,7 +32060,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>Một vết nứt bí ẩn đột nhiên xuất hiện sâu trong mỏ. Trong Sonoro Sphere đặc biệt này, những hợp kim do Shilang rèn tạo sẽ mang đến sự trợ giúp bất ngờ cho bạn.</t>
+          <t>Một vết nứt bí ẩn đột nhiên xuất hiện sâu trong mỏ. Trong Sonoro Sphere đặc biệt này, những hợp kim do Shilang rèn tạo lại mang đến sự trợ giúp bất ngờ cho cậu.</t>
         </is>
       </c>
     </row>
@@ -32125,7 +32125,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>Khe Nứt Hư Ảo</t>
+          <t>Khe Nứt Hư Không</t>
         </is>
       </c>
     </row>
@@ -32190,7 +32190,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>Một vết nứt bí ẩn đột nhiên xuất hiện sâu trong mỏ. Trong Sonoro Sphere đặc biệt này, những hợp kim do Shilang rèn tạo sẽ mang đến sự trợ giúp bất ngờ cho bạn.</t>
+          <t>Một vết nứt bí ẩn đột nhiên xuất hiện sâu trong mỏ. Trong Sonoro Sphere đặc biệt này, những hợp kim do Shilang rèn tạo lại mang đến sự trợ giúp bất ngờ cho cậu.</t>
         </is>
       </c>
     </row>
@@ -32255,7 +32255,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Khe Nứt Vĩnh Hằng</t>
+          <t>Vết Nứt Vĩnh Cửu</t>
         </is>
       </c>
     </row>
@@ -32320,7 +32320,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>Một vết nứt bí ẩn đột nhiên xuất hiện sâu trong mỏ. Trong Sonoro Sphere đặc biệt này, các hợp kim do Shilang rèn sẽ hỗ trợ bạn một cách bất ngờ.</t>
+          <t>Một vết nứt bí ẩn đột nhiên xuất hiện sâu trong lòng mỏ. Trong Sonoro Sphere đặc biệt này, những hợp kim do Shilang rèn tạo lại mang đến sự trợ giúp bất ngờ cho cậu.</t>
         </is>
       </c>
     </row>
@@ -32385,7 +32385,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>Khe Nứt Vỡ Tan</t>
+          <t>Vết Rạn Đứt Gãy</t>
         </is>
       </c>
     </row>
@@ -32450,7 +32450,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>Một vết nứt bí ẩn đột nhiên xuất hiện sâu trong mỏ. Trong Sonoro Sphere đặc biệt này, các hợp kim do Shilang rèn sẽ hỗ trợ bạn một cách bất ngờ.</t>
+          <t>Một vết nứt bí ẩn đột nhiên xuất hiện sâu trong lòng mỏ. Trong Sonoro Sphere đặc biệt này, những hợp kim do Shilang rèn tạo lại mang đến sự trợ giúp bất ngờ cho cậu.</t>
         </is>
       </c>
     </row>
@@ -32515,7 +32515,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Khe Nứt Thiên Giới</t>
+          <t>Khe Nứt Empyrean</t>
         </is>
       </c>
     </row>
@@ -32580,7 +32580,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>Một vết nứt bí ẩn đột nhiên xuất hiện sâu trong mỏ. Trong Sonoro Sphere đặc biệt này, các hợp kim do Shilang rèn sẽ hỗ trợ bạn một cách bất ngờ.</t>
+          <t>Một vết nứt bí ẩn đột nhiên xuất hiện sâu trong lòng mỏ. Trong Sonoro Sphere đặc biệt này, những hợp kim do Shilang rèn tạo lại mang đến sự trợ giúp bất ngờ cho cậu.</t>
         </is>
       </c>
     </row>
@@ -32645,7 +32645,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>Khe Vực Aftersound</t>
+          <t>Khe Nứt Dư Âm</t>
         </is>
       </c>
     </row>
@@ -32710,7 +32710,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Một vết nứt bí ẩn đột nhiên xuất hiện sâu trong mỏ. Trong Sonoro Sphere đặc biệt này, các hợp kim do Shilang rèn sẽ hỗ trợ bạn một cách bất ngờ.</t>
+          <t>Một vết nứt bí ẩn đột nhiên xuất hiện sâu trong lòng mỏ. Trong Sonoro Sphere đặc biệt này, những hợp kim do Shilang rèn tạo lại mang đến sự trợ giúp bất ngờ cho cậu.</t>
         </is>
       </c>
     </row>
@@ -32775,7 +32775,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>Khe Nứt Nhiệt Huyết</t>
+          <t>Vết Nứt Nhiệt Huyết</t>
         </is>
       </c>
     </row>
@@ -32840,7 +32840,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>Một vết nứt bí ẩn đột nhiên xuất hiện sâu trong mỏ. Trong Sonoro Sphere đặc biệt này, các hợp kim do Shilang rèn sẽ hỗ trợ bạn một cách bất ngờ.</t>
+          <t>Một vết nứt bí ẩn đột nhiên xuất hiện sâu trong lòng mỏ. Trong Sonoro Sphere đặc biệt này, những hợp kim do Shilang rèn tạo lại mang đến sự trợ giúp bất ngờ cho cậu.</t>
         </is>
       </c>
     </row>
@@ -32970,7 +32970,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Một vết nứt bí ẩn đột nhiên xuất hiện sâu trong mỏ. Trong Sonoro Sphere đặc biệt này, các hợp kim do Shilang rèn sẽ hỗ trợ bạn một cách bất ngờ.</t>
+          <t>Một vết nứt bí ẩn đột nhiên xuất hiện sâu trong lòng mỏ. Trong Sonoro Sphere đặc biệt này, những hợp kim do Shilang rèn tạo lại mang đến sự trợ giúp bất ngờ cho cậu.</t>
         </is>
       </c>
     </row>
@@ -33035,7 +33035,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>Khe Nứt Trì Trệ</t>
+          <t>Vết Nứt Trì Trệ</t>
         </is>
       </c>
     </row>
